--- a/04_Figures/F06_prediction/modules/T3/lasso/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/T3/lasso/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -146,43 +146,37 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">ME_green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_magenta</t>
+  </si>
+  <si>
     <t xml:space="preserve">ME_purple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_greenyellow</t>
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_green</t>
+    <t xml:space="preserve">ME_turquoise</t>
   </si>
   <si>
     <t xml:space="preserve">ME_black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_greenyellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_magenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_yellow</t>
   </si>
 </sst>
 </file>
@@ -569,13 +563,13 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.24396954861589</v>
+        <v>-0.452695252005031</v>
       </c>
       <c r="I2" t="n">
         <v>-0.585714285714286</v>
@@ -602,28 +596,28 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.24396954861589</v>
+        <v>-0.452695252005031</v>
       </c>
       <c r="I3" t="n">
         <v>-0.585714285714286</v>
       </c>
       <c r="J3" t="n">
-        <v>0.686567164179104</v>
+        <v>0.830845771144279</v>
       </c>
       <c r="K3" t="n">
-        <v>0.154228855721393</v>
+        <v>0.109452736318408</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.385372182776368</v>
+        <v>-1.92660505239227</v>
       </c>
       <c r="M3" t="n">
-        <v>0.972253983742444</v>
+        <v>9.61211147148642</v>
       </c>
     </row>
     <row r="4">
@@ -643,13 +637,13 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.503618906597997</v>
+        <v>-0.621482255760033</v>
       </c>
       <c r="I4" t="n">
         <v>-0.925</v>
@@ -676,28 +670,28 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.503618906597997</v>
+        <v>-0.621482255760033</v>
       </c>
       <c r="I5" t="n">
         <v>-0.925</v>
       </c>
       <c r="J5" t="n">
-        <v>0.81592039800995</v>
+        <v>0.850746268656716</v>
       </c>
       <c r="K5" t="n">
-        <v>0.253731343283582</v>
+        <v>0.308457711442786</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.53295165900195</v>
+        <v>-2.10462527044896</v>
       </c>
       <c r="M5" t="n">
-        <v>1.51713307175862</v>
+        <v>9.53828958420609</v>
       </c>
     </row>
     <row r="6">
@@ -717,16 +711,16 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.170703624241288</v>
+        <v>-1.09052305283893</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>-0.964285714285714</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -750,28 +744,28 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.170703624241288</v>
+        <v>-1.09052305283893</v>
       </c>
       <c r="I7" t="n">
-        <v>-1</v>
+        <v>-0.964285714285714</v>
       </c>
       <c r="J7" t="n">
-        <v>0.512437810945274</v>
+        <v>0.940298507462687</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.308457711442786</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.527105252548397</v>
+        <v>-1.53045279136893</v>
       </c>
       <c r="M7" t="n">
-        <v>1.57540806569832</v>
+        <v>6.87804531804563</v>
       </c>
     </row>
     <row r="8">
@@ -791,13 +785,13 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.212671407790479</v>
+        <v>-0.212710465069593</v>
       </c>
       <c r="I8" t="n">
         <v>-0.792857142857143</v>
@@ -824,28 +818,28 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.212671407790479</v>
+        <v>-0.212710465069593</v>
       </c>
       <c r="I9" t="n">
         <v>-0.792857142857143</v>
       </c>
       <c r="J9" t="n">
-        <v>0.621890547263682</v>
+        <v>0.606965174129353</v>
       </c>
       <c r="K9" t="n">
-        <v>0.199004975124378</v>
+        <v>0.18407960199005</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.341283492544157</v>
+        <v>-2.58890238919452</v>
       </c>
       <c r="M9" t="n">
-        <v>0.562073763733924</v>
+        <v>12.3490756031855</v>
       </c>
     </row>
     <row r="10">
@@ -865,7 +859,7 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -898,7 +892,7 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
@@ -910,16 +904,16 @@
         <v>-0.996415759077198</v>
       </c>
       <c r="J11" t="n">
-        <v>0.203980099502488</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="K11" t="n">
-        <v>0.676616915422886</v>
+        <v>0.6318407960199</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.737798759335399</v>
+        <v>-1.15789904623269</v>
       </c>
       <c r="M11" t="n">
-        <v>3.01062305006001</v>
+        <v>6.99960667335483</v>
       </c>
     </row>
     <row r="12">
@@ -939,16 +933,16 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.349540493144532</v>
       </c>
       <c r="I12" t="n">
-        <v>-1</v>
+        <v>-0.998898071290657</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -972,28 +966,28 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.349540493144532</v>
       </c>
       <c r="I13" t="n">
-        <v>-1</v>
+        <v>-0.998898071290657</v>
       </c>
       <c r="J13" t="n">
-        <v>0.432835820895522</v>
+        <v>0.721393034825871</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.800995024875622</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.322145524775003</v>
+        <v>-2.33747363254488</v>
       </c>
       <c r="M13" t="n">
-        <v>0.508584932046621</v>
+        <v>10.4326321356703</v>
       </c>
     </row>
   </sheetData>
@@ -1026,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.133783276233125</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="3">
@@ -1048,7 +1042,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0133961784656675</v>
+        <v>0.0770261651673058</v>
       </c>
     </row>
     <row r="5">
@@ -1059,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-6.17779443077345</v>
+        <v>-30.0542415339638</v>
       </c>
     </row>
     <row r="6">
@@ -1070,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.505066826422281</v>
+        <v>-0.16995087538795</v>
       </c>
     </row>
     <row r="7">
@@ -1092,7 +1086,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.14795918367347</v>
+        <v>-28.4795814832603</v>
       </c>
     </row>
     <row r="9">
@@ -1103,7 +1097,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.202264274129232</v>
       </c>
     </row>
     <row r="10">
@@ -1136,7 +1130,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.297836582965963</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="13">
@@ -1147,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.201157879964266</v>
+        <v>-0.23440629285358</v>
       </c>
     </row>
     <row r="14">
@@ -1158,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.337233873340641</v>
+        <v>-0.197895876285322</v>
       </c>
     </row>
     <row r="15">
@@ -1180,7 +1174,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.178995873998964</v>
+        <v>-0.11608512522944</v>
       </c>
     </row>
     <row r="17">
@@ -1191,7 +1185,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.178283141932582</v>
       </c>
     </row>
     <row r="18">
@@ -1202,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.183115583862542</v>
+        <v>-3.70980969452554</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.3683921613027</v>
+        <v>-0.427304994501954</v>
       </c>
     </row>
     <row r="20">
@@ -1224,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.277666027884965</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="21">
@@ -1235,7 +1229,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.290965955952977</v>
       </c>
     </row>
     <row r="22">
@@ -1246,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.204195558141023</v>
       </c>
     </row>
     <row r="23">
@@ -1257,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.326713782804421</v>
       </c>
     </row>
     <row r="24">
@@ -1301,7 +1295,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.274334142630129</v>
+        <v>-0.0542384207851161</v>
       </c>
     </row>
     <row r="28">
@@ -1323,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.236557493833219</v>
       </c>
     </row>
     <row r="30">
@@ -1356,7 +1350,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.201936996117861</v>
+        <v>-0.333456742759846</v>
       </c>
     </row>
     <row r="33">
@@ -1367,7 +1361,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.918344358164403</v>
       </c>
     </row>
     <row r="34">
@@ -1378,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.300831067644912</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="35">
@@ -1389,7 +1383,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.87152734532446</v>
+        <v>-2.12372278149493</v>
       </c>
     </row>
     <row r="36">
@@ -1400,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.384672399889013</v>
+        <v>-0.401233124695312</v>
       </c>
     </row>
     <row r="37">
@@ -1411,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>0.374276034311487</v>
+        <v>0.3318738994336</v>
       </c>
     </row>
     <row r="38">
@@ -1422,7 +1416,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.153164929131474</v>
+        <v>-0.359976139991716</v>
       </c>
     </row>
     <row r="39">
@@ -1433,7 +1427,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.268376140332834</v>
       </c>
     </row>
     <row r="40">
@@ -1444,7 +1438,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.160425745623453</v>
       </c>
     </row>
     <row r="41">
@@ -1455,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.445597364323215</v>
+        <v>-0.430656418514853</v>
       </c>
     </row>
     <row r="42">
@@ -1466,7 +1460,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.463643512593366</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="43">
@@ -1477,7 +1471,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.3563905975293</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="44">
@@ -1488,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.906657539746457</v>
       </c>
     </row>
     <row r="45">
@@ -1499,7 +1493,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.504572901049746</v>
       </c>
     </row>
     <row r="46">
@@ -1510,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.333864471076465</v>
+        <v>-0.158276912439771</v>
       </c>
     </row>
     <row r="47">
@@ -1543,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.132075807133404</v>
+        <v>-0.102597908604342</v>
       </c>
     </row>
     <row r="50">
@@ -1554,7 +1548,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.183100086960843</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="51">
@@ -1565,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.384037093173226</v>
+        <v>-1.11234510213699</v>
       </c>
     </row>
     <row r="52">
@@ -1576,7 +1570,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.874100058719349</v>
+        <v>-0.246798737691654</v>
       </c>
     </row>
     <row r="53">
@@ -1587,7 +1581,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>0.394942413633147</v>
+        <v>0.432425179300548</v>
       </c>
     </row>
     <row r="54">
@@ -1598,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>0.332481621758734</v>
+        <v>0.287503043587693</v>
       </c>
     </row>
     <row r="55">
@@ -1609,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.758350504978949</v>
       </c>
     </row>
     <row r="56">
@@ -1631,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.688502977819581</v>
+        <v>-0.435275024321439</v>
       </c>
     </row>
     <row r="58">
@@ -1642,7 +1636,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-1.23612384388577</v>
+        <v>-1.74780739847843</v>
       </c>
     </row>
     <row r="59">
@@ -1653,7 +1647,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.214287531391987</v>
+        <v>-0.219060665842569</v>
       </c>
     </row>
     <row r="60">
@@ -1675,7 +1669,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.161986410274114</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="62">
@@ -1686,7 +1680,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.36978259290343</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="63">
@@ -1697,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-2.95007065436939</v>
+        <v>-0.392057186703541</v>
       </c>
     </row>
     <row r="64">
@@ -1708,7 +1702,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.330122625264074</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="65">
@@ -1719,7 +1713,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.151263569489238</v>
+        <v>-0.179387471505077</v>
       </c>
     </row>
     <row r="66">
@@ -1730,7 +1724,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.34854881384443</v>
+        <v>-5.9822059650861</v>
       </c>
     </row>
     <row r="67">
@@ -1741,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.397687337853005</v>
+        <v>-0.305862686568005</v>
       </c>
     </row>
     <row r="68">
@@ -1763,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.203646277723016</v>
       </c>
     </row>
     <row r="70">
@@ -1785,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.248322443492154</v>
+        <v>-0.200101947496921</v>
       </c>
     </row>
     <row r="72">
@@ -1796,7 +1790,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.463939850159708</v>
+        <v>-0.966993337114241</v>
       </c>
     </row>
     <row r="73">
@@ -1807,7 +1801,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.14795918367347</v>
+        <v>-47.0968958676503</v>
       </c>
     </row>
     <row r="74">
@@ -1818,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.184309379190748</v>
+        <v>-0.196773979962668</v>
       </c>
     </row>
     <row r="75">
@@ -1829,7 +1823,7 @@
         <v>16</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.192600699586128</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="76">
@@ -1840,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.328631811654204</v>
+        <v>-0.35721049334564</v>
       </c>
     </row>
     <row r="77">
@@ -1862,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.0824336157238472</v>
+        <v>-42.6713930811119</v>
       </c>
     </row>
     <row r="79">
@@ -1884,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.367815679019958</v>
+        <v>-0.503419192131671</v>
       </c>
     </row>
     <row r="81">
@@ -1895,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.41088993031236</v>
+        <v>-0.331063645465123</v>
       </c>
     </row>
     <row r="82">
@@ -1906,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.244993901227887</v>
+        <v>-0.211430343181434</v>
       </c>
     </row>
     <row r="83">
@@ -1917,7 +1911,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.406967976281171</v>
+        <v>-0.304960508319974</v>
       </c>
     </row>
     <row r="84">
@@ -1928,7 +1922,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.366045579177114</v>
       </c>
     </row>
     <row r="85">
@@ -1939,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.0224273947452296</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="86">
@@ -1950,7 +1944,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.160853755468067</v>
+        <v>-0.20473974673817</v>
       </c>
     </row>
     <row r="87">
@@ -1961,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.479246292470924</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="88">
@@ -1972,7 +1966,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.219342407088561</v>
+        <v>-0.20676169188104</v>
       </c>
     </row>
     <row r="89">
@@ -1983,7 +1977,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.11128414572622</v>
       </c>
     </row>
     <row r="90">
@@ -1994,7 +1988,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.159350899357731</v>
+        <v>-0.139385113836726</v>
       </c>
     </row>
     <row r="91">
@@ -2005,7 +1999,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.398787293409081</v>
+        <v>-0.316921581604592</v>
       </c>
     </row>
     <row r="92">
@@ -2016,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.667432374190732</v>
+        <v>-0.558661962803652</v>
       </c>
     </row>
     <row r="93">
@@ -2038,7 +2032,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>0.299796984057481</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="95">
@@ -2049,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.359176557116807</v>
+        <v>-0.839785576307705</v>
       </c>
     </row>
     <row r="96">
@@ -2060,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.295365269403091</v>
       </c>
     </row>
     <row r="97">
@@ -2071,7 +2065,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.228407791231741</v>
       </c>
     </row>
     <row r="98">
@@ -2082,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.329712106675992</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="99">
@@ -2093,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.633772705232368</v>
+        <v>-0.543821093344166</v>
       </c>
     </row>
     <row r="100">
@@ -2104,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.639662888429994</v>
+        <v>-105.75575373304</v>
       </c>
     </row>
     <row r="101">
@@ -2115,7 +2109,7 @@
         <v>16</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.84312887729655</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="102">
@@ -2126,7 +2120,7 @@
         <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.471221420451433</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="103">
@@ -2137,7 +2131,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.182612402927409</v>
+        <v>-0.103085639089304</v>
       </c>
     </row>
     <row r="104">
@@ -2148,7 +2142,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.196556970114489</v>
+        <v>-0.23781075759425</v>
       </c>
     </row>
     <row r="105">
@@ -2170,7 +2164,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.201405769337947</v>
+        <v>-0.193381932270763</v>
       </c>
     </row>
     <row r="107">
@@ -2181,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.315771344505958</v>
       </c>
     </row>
     <row r="108">
@@ -2192,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.159750261672402</v>
       </c>
     </row>
     <row r="109">
@@ -2214,7 +2208,7 @@
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.168863341772888</v>
       </c>
     </row>
     <row r="111">
@@ -2225,7 +2219,7 @@
         <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.197754508018954</v>
+        <v>-0.211824998171862</v>
       </c>
     </row>
     <row r="112">
@@ -2269,7 +2263,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.259384074602608</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="116">
@@ -2302,7 +2296,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.819744611795541</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="119">
@@ -2324,7 +2318,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.363551403346587</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="121">
@@ -2357,7 +2351,7 @@
         <v>16</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.363485735548591</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="124">
@@ -2368,7 +2362,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.187727905774889</v>
+        <v>-41.6220895546249</v>
       </c>
     </row>
     <row r="125">
@@ -2379,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.381766890527521</v>
+        <v>-0.298062100269579</v>
       </c>
     </row>
     <row r="126">
@@ -2390,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.532780976161408</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="127">
@@ -2401,7 +2395,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.213656487642137</v>
+        <v>-0.269817986029444</v>
       </c>
     </row>
     <row r="128">
@@ -2412,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.15974677932114</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="129">
@@ -2445,7 +2439,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.0184332212534843</v>
+        <v>-0.793099101115873</v>
       </c>
     </row>
     <row r="132">
@@ -2456,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.197448490803599</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="133">
@@ -2478,7 +2472,7 @@
         <v>16</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.77108881744254</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2505,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.543838051334065</v>
+        <v>-0.152397830685301</v>
       </c>
     </row>
     <row r="138">
@@ -2522,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.166523964193846</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="139">
@@ -2533,7 +2527,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.232756660833527</v>
+        <v>-0.387022213708877</v>
       </c>
     </row>
     <row r="140">
@@ -2544,7 +2538,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.185377723565118</v>
+        <v>-0.155815035210277</v>
       </c>
     </row>
     <row r="141">
@@ -2555,7 +2549,7 @@
         <v>16</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.210680073116296</v>
+        <v>-0.0870904049335768</v>
       </c>
     </row>
     <row r="142">
@@ -2577,7 +2571,7 @@
         <v>16</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.109546428552916</v>
+        <v>0.139141020093841</v>
       </c>
     </row>
     <row r="144">
@@ -2599,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.197003010148258</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="146">
@@ -2610,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.109817925982914</v>
+        <v>-0.133475664733682</v>
       </c>
     </row>
     <row r="147">
@@ -2621,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-7.00199473200054</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="148">
@@ -2643,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.440075912476498</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="150">
@@ -2654,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.361068921363768</v>
+        <v>-0.48857202210892</v>
       </c>
     </row>
     <row r="151">
@@ -2665,7 +2659,7 @@
         <v>16</v>
       </c>
       <c r="C151" t="n">
-        <v>-9.37551497237401</v>
+        <v>-17.9119459448101</v>
       </c>
     </row>
     <row r="152">
@@ -2698,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.144383220745611</v>
+        <v>-0.246073127933225</v>
       </c>
     </row>
     <row r="155">
@@ -2709,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.38443003643904</v>
+        <v>-0.26077331116459</v>
       </c>
     </row>
     <row r="156">
@@ -2720,7 +2714,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-1.17439741492393</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="157">
@@ -2731,7 +2725,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.16904096483676</v>
+        <v>-0.36546871775045</v>
       </c>
     </row>
     <row r="158">
@@ -2753,7 +2747,7 @@
         <v>16</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.224819062871491</v>
+        <v>-5.80837312892496</v>
       </c>
     </row>
     <row r="160">
@@ -2775,7 +2769,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.236783758714239</v>
+        <v>-0.157311865076428</v>
       </c>
     </row>
     <row r="162">
@@ -2786,7 +2780,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>-1.38661660235775</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="163">
@@ -2797,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.268210211805536</v>
+        <v>-3.498517657819</v>
       </c>
     </row>
     <row r="164">
@@ -2808,7 +2802,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.1879306789904</v>
+        <v>-0.187974268803244</v>
       </c>
     </row>
     <row r="165">
@@ -2819,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.226273970122908</v>
+        <v>-0.177683998853033</v>
       </c>
     </row>
     <row r="166">
@@ -2830,7 +2824,7 @@
         <v>16</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.45533312975659</v>
       </c>
     </row>
     <row r="167">
@@ -2841,7 +2835,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="n">
-        <v>-2.61266647300393</v>
+        <v>-0.218552059259541</v>
       </c>
     </row>
     <row r="168">
@@ -2863,7 +2857,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.94474811499437</v>
       </c>
     </row>
     <row r="170">
@@ -2874,7 +2868,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.160198901310594</v>
+        <v>-0.423119399730327</v>
       </c>
     </row>
     <row r="171">
@@ -2896,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.164044189557641</v>
+        <v>-0.17696244814459</v>
       </c>
     </row>
     <row r="173">
@@ -2929,7 +2923,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.508465394998606</v>
+        <v>-0.535834665827913</v>
       </c>
     </row>
     <row r="176">
@@ -2940,7 +2934,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.586458729400374</v>
+        <v>-0.20884495136689</v>
       </c>
     </row>
     <row r="177">
@@ -2951,7 +2945,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.190442602749948</v>
+        <v>-0.234938035989284</v>
       </c>
     </row>
     <row r="178">
@@ -2984,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.186202053982765</v>
+        <v>-0.432801061968322</v>
       </c>
     </row>
     <row r="181">
@@ -2995,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>0.601160243508648</v>
+        <v>0.0658532752066783</v>
       </c>
     </row>
     <row r="182">
@@ -3006,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.375253833403556</v>
+        <v>-0.19094081571924</v>
       </c>
     </row>
     <row r="183">
@@ -3017,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.00231404427306869</v>
+        <v>-1.14517979666578</v>
       </c>
     </row>
     <row r="184">
@@ -3039,7 +3033,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.206041364065194</v>
+        <v>-0.203417421848935</v>
       </c>
     </row>
     <row r="186">
@@ -3050,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.525603236009909</v>
+        <v>-0.459932586610266</v>
       </c>
     </row>
     <row r="187">
@@ -3061,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.199958489114882</v>
+        <v>-0.304713889187741</v>
       </c>
     </row>
     <row r="188">
@@ -3072,7 +3066,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.427192487519008</v>
+        <v>-0.407946889044571</v>
       </c>
     </row>
     <row r="189">
@@ -3083,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.220260252653003</v>
+        <v>-0.185271729031027</v>
       </c>
     </row>
     <row r="190">
@@ -3094,7 +3088,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.504958956704452</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="191">
@@ -3105,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.262763556379916</v>
+        <v>-0.624248950306843</v>
       </c>
     </row>
     <row r="192">
@@ -3116,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.343545344766419</v>
+        <v>-0.358012999275578</v>
       </c>
     </row>
     <row r="193">
@@ -3160,7 +3154,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>0.0765450519025237</v>
+        <v>-3.46889671927935</v>
       </c>
     </row>
     <row r="197">
@@ -3171,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.171766846082664</v>
+        <v>0.0862261718026235</v>
       </c>
     </row>
     <row r="198">
@@ -3204,7 +3198,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.195973825057307</v>
+        <v>-0.20494378302701</v>
       </c>
     </row>
     <row r="201">
@@ -3215,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="C201" t="n">
-        <v>0.189498894855587</v>
+        <v>-0.275984227777083</v>
       </c>
     </row>
     <row r="202">
@@ -3237,7 +3231,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-17.2713990380526</v>
+        <v>-58.903279317683</v>
       </c>
     </row>
     <row r="204">
@@ -3248,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.6364311798184</v>
+        <v>-0.464990477283484</v>
       </c>
     </row>
     <row r="205">
@@ -3259,7 +3253,7 @@
         <v>16</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.14795918367347</v>
+        <v>-68.0651434677198</v>
       </c>
     </row>
     <row r="206">
@@ -3270,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.0987326322097231</v>
+        <v>-1.15616912695679</v>
       </c>
     </row>
     <row r="207">
@@ -3292,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-1.83287840674642</v>
+        <v>-0.349154670475928</v>
       </c>
     </row>
     <row r="209">
@@ -3303,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-3.5319110096671</v>
+        <v>-0.168772545046089</v>
       </c>
     </row>
     <row r="210">
@@ -3314,7 +3308,7 @@
         <v>16</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.18105963809993</v>
       </c>
     </row>
     <row r="211">
@@ -3336,7 +3330,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.34401848333751</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="213">
@@ -3347,7 +3341,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.205327060855568</v>
       </c>
     </row>
     <row r="214">
@@ -3358,7 +3352,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.606596143581554</v>
+        <v>-0.558648472533708</v>
       </c>
     </row>
     <row r="215">
@@ -3402,7 +3396,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>0.139033580846117</v>
+        <v>-0.228310173648361</v>
       </c>
     </row>
     <row r="219">
@@ -3413,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.453683860707009</v>
+        <v>-0.0745069988783915</v>
       </c>
     </row>
     <row r="220">
@@ -3424,7 +3418,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.304118370644612</v>
+        <v>-0.283667569463957</v>
       </c>
     </row>
     <row r="221">
@@ -3435,7 +3429,7 @@
         <v>16</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.265349027646236</v>
       </c>
     </row>
     <row r="222">
@@ -3446,7 +3440,7 @@
         <v>16</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.200458053343595</v>
+        <v>-0.23103885421009</v>
       </c>
     </row>
     <row r="223">
@@ -3457,7 +3451,7 @@
         <v>16</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.50845216645187</v>
+        <v>-0.66366833600213</v>
       </c>
     </row>
     <row r="224">
@@ -3468,7 +3462,7 @@
         <v>16</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.196272691138282</v>
+        <v>-0.196537888346628</v>
       </c>
     </row>
     <row r="225">
@@ -3501,7 +3495,7 @@
         <v>16</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.385723395090904</v>
+        <v>-0.476988338381317</v>
       </c>
     </row>
     <row r="228">
@@ -3556,7 +3550,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.317216447076857</v>
+        <v>-0.373308141510494</v>
       </c>
     </row>
     <row r="233">
@@ -3578,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.176801982114354</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="235">
@@ -3589,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.608564539648957</v>
+        <v>-0.356332552847084</v>
       </c>
     </row>
     <row r="236">
@@ -3600,7 +3594,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.508009530671655</v>
+        <v>-0.319981937837065</v>
       </c>
     </row>
     <row r="237">
@@ -3611,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.265216542295478</v>
+        <v>0.16766367434088</v>
       </c>
     </row>
     <row r="238">
@@ -3622,7 +3616,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.276087657367033</v>
+        <v>-0.300751963248864</v>
       </c>
     </row>
     <row r="239">
@@ -3655,7 +3649,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.517893159383205</v>
+        <v>-0.85440505535023</v>
       </c>
     </row>
     <row r="242">
@@ -3677,7 +3671,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.300078434145991</v>
+        <v>-0.255651493583436</v>
       </c>
     </row>
     <row r="244">
@@ -3688,7 +3682,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.174288801859722</v>
+        <v>-0.0351265354183035</v>
       </c>
     </row>
     <row r="245">
@@ -3710,7 +3704,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.185204327630753</v>
       </c>
     </row>
     <row r="247">
@@ -3743,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.285206457149949</v>
+        <v>-0.205913909218014</v>
       </c>
     </row>
     <row r="250">
@@ -3754,7 +3748,7 @@
         <v>16</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.259339387420976</v>
+        <v>-0.179051633124321</v>
       </c>
     </row>
     <row r="251">
@@ -3765,7 +3759,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.504940076464501</v>
+        <v>-0.396716571030564</v>
       </c>
     </row>
     <row r="252">
@@ -3776,7 +3770,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="n">
-        <v>0.169081648883648</v>
+        <v>-0.20902238832396</v>
       </c>
     </row>
     <row r="253">
@@ -3787,7 +3781,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>0.176170657102805</v>
+        <v>-0.0356029732570942</v>
       </c>
     </row>
     <row r="254">
@@ -3798,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.196255598935389</v>
+        <v>-0.178130959556249</v>
       </c>
     </row>
     <row r="255">
@@ -3820,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.508589745305697</v>
+        <v>-0.353475114056692</v>
       </c>
     </row>
     <row r="257">
@@ -3831,7 +3825,7 @@
         <v>16</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.340886439177983</v>
       </c>
     </row>
     <row r="258">
@@ -3875,7 +3869,7 @@
         <v>16</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.202961790699588</v>
+        <v>-0.134390242383806</v>
       </c>
     </row>
     <row r="262">
@@ -3886,7 +3880,7 @@
         <v>16</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.693927635491385</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="263">
@@ -3897,7 +3891,7 @@
         <v>16</v>
       </c>
       <c r="C263" t="n">
-        <v>-2.16672113666646</v>
+        <v>-9.0392048037114</v>
       </c>
     </row>
     <row r="264">
@@ -3919,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.160169463430745</v>
+        <v>-0.15475311278123</v>
       </c>
     </row>
     <row r="266">
@@ -3930,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.463047817138786</v>
+        <v>-0.386418878864084</v>
       </c>
     </row>
     <row r="267">
@@ -3941,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.331503207863204</v>
+        <v>-13.3222653872281</v>
       </c>
     </row>
     <row r="268">
@@ -3952,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.201184103469338</v>
+        <v>-0.376531619561862</v>
       </c>
     </row>
     <row r="269">
@@ -3974,7 +3968,7 @@
         <v>16</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.160495255814995</v>
       </c>
     </row>
     <row r="271">
@@ -3996,7 +3990,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.14403292420285</v>
       </c>
     </row>
     <row r="273">
@@ -4018,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.277233508185465</v>
+        <v>-0.175335596657081</v>
       </c>
     </row>
     <row r="275">
@@ -4029,7 +4023,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-5.75475487320706</v>
+        <v>-0.23633948174193</v>
       </c>
     </row>
     <row r="276">
@@ -4040,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.496207476447218</v>
+        <v>-1.16092527657262</v>
       </c>
     </row>
     <row r="277">
@@ -4051,7 +4045,7 @@
         <v>16</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.24202150024431</v>
       </c>
     </row>
     <row r="278">
@@ -4062,7 +4056,7 @@
         <v>16</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.14795918367347</v>
+        <v>-21.9866075344528</v>
       </c>
     </row>
     <row r="279">
@@ -4084,7 +4078,7 @@
         <v>16</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.164838029769552</v>
       </c>
     </row>
     <row r="281">
@@ -4095,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.0145449502486239</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="282">
@@ -4117,7 +4111,7 @@
         <v>16</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.669388353548377</v>
+        <v>-0.309011943663639</v>
       </c>
     </row>
     <row r="284">
@@ -4128,7 +4122,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.244725597996706</v>
+        <v>-0.268492812442804</v>
       </c>
     </row>
     <row r="285">
@@ -4139,7 +4133,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.680757008211142</v>
+        <v>-0.581887220648636</v>
       </c>
     </row>
     <row r="286">
@@ -4150,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.154238083247215</v>
+        <v>-0.39320999856526</v>
       </c>
     </row>
     <row r="287">
@@ -4161,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.212591919652394</v>
       </c>
     </row>
     <row r="288">
@@ -4172,7 +4166,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.236907177734491</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="289">
@@ -4194,7 +4188,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.284463931935788</v>
+        <v>-0.0136462061633906</v>
       </c>
     </row>
     <row r="291">
@@ -4205,7 +4199,7 @@
         <v>16</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.208193188118183</v>
+        <v>-0.249533506282469</v>
       </c>
     </row>
     <row r="292">
@@ -4216,7 +4210,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.507665953984678</v>
+        <v>-24.999260104116</v>
       </c>
     </row>
     <row r="293">
@@ -4238,7 +4232,7 @@
         <v>16</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.189483564281397</v>
+        <v>-0.85852879947262</v>
       </c>
     </row>
     <row r="295">
@@ -4249,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.223519596643394</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="296">
@@ -4260,7 +4254,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>-5.50984372181037</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="297">
@@ -4293,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.228939375772627</v>
+        <v>-0.281072052610414</v>
       </c>
     </row>
     <row r="300">
@@ -4304,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.68562681354949</v>
+        <v>-49.6752814391346</v>
       </c>
     </row>
     <row r="301">
@@ -4326,7 +4320,7 @@
         <v>16</v>
       </c>
       <c r="C302" t="n">
-        <v>-3.41653415820315</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="303">
@@ -4337,7 +4331,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.670387086798054</v>
+        <v>-0.789792110176668</v>
       </c>
     </row>
     <row r="304">
@@ -4348,7 +4342,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.242417718444416</v>
+        <v>-0.315763151027045</v>
       </c>
     </row>
     <row r="305">
@@ -4403,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.580266766842378</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="310">
@@ -4414,7 +4408,7 @@
         <v>16</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.182605153362337</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="311">
@@ -4425,7 +4419,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.343883714675182</v>
       </c>
     </row>
     <row r="312">
@@ -4436,7 +4430,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.147959183673469</v>
+        <v>-68.0241068981597</v>
       </c>
     </row>
     <row r="313">
@@ -4458,7 +4452,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.32026310556588</v>
       </c>
     </row>
     <row r="315">
@@ -4513,7 +4507,7 @@
         <v>16</v>
       </c>
       <c r="C319" t="n">
-        <v>-7.01620869184626</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="320">
@@ -4524,7 +4518,7 @@
         <v>16</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.804089291882363</v>
       </c>
     </row>
     <row r="321">
@@ -4546,7 +4540,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.200096195634155</v>
+        <v>-0.21953856251663</v>
       </c>
     </row>
     <row r="323">
@@ -4579,7 +4573,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.627661419910889</v>
+        <v>0.345742290902645</v>
       </c>
     </row>
     <row r="326">
@@ -4590,7 +4584,7 @@
         <v>16</v>
       </c>
       <c r="C326" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.467904611546763</v>
       </c>
     </row>
     <row r="327">
@@ -4601,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.29169816981121</v>
+        <v>-0.66916182586561</v>
       </c>
     </row>
     <row r="328">
@@ -4612,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.439289064430843</v>
+        <v>-0.511610905380129</v>
       </c>
     </row>
     <row r="329">
@@ -4645,7 +4639,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>0.117567298195525</v>
+        <v>-0.212884735681983</v>
       </c>
     </row>
     <row r="332">
@@ -4656,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.470405498394053</v>
+        <v>-0.634291188528699</v>
       </c>
     </row>
     <row r="333">
@@ -4667,7 +4661,7 @@
         <v>16</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.229773213551451</v>
+        <v>-0.738907600267264</v>
       </c>
     </row>
     <row r="334">
@@ -4678,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.589188288998875</v>
       </c>
     </row>
     <row r="335">
@@ -4689,7 +4683,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.526355939009685</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="336">
@@ -4700,7 +4694,7 @@
         <v>16</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.773663715369749</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="337">
@@ -4722,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>0.0272476025630238</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="339">
@@ -4733,7 +4727,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.296760339352425</v>
+        <v>-0.298773195995304</v>
       </c>
     </row>
     <row r="340">
@@ -4744,7 +4738,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.265147487558208</v>
+        <v>-0.266902181899777</v>
       </c>
     </row>
     <row r="341">
@@ -4755,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.17782011936141</v>
       </c>
     </row>
     <row r="342">
@@ -4766,7 +4760,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.241577386015539</v>
       </c>
     </row>
     <row r="343">
@@ -4777,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.371242102132833</v>
+        <v>-2.72622523136733</v>
       </c>
     </row>
     <row r="344">
@@ -4810,7 +4804,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.198067449091898</v>
+        <v>-0.191643383292648</v>
       </c>
     </row>
     <row r="347">
@@ -4821,7 +4815,7 @@
         <v>16</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.934210452281957</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="348">
@@ -4832,7 +4826,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.660586196914286</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="349">
@@ -4854,7 +4848,7 @@
         <v>16</v>
       </c>
       <c r="C350" t="n">
-        <v>-1.2570974277458</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="351">
@@ -4865,7 +4859,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.367890293219907</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="352">
@@ -4876,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.290632527460083</v>
+        <v>-0.48095969654598</v>
       </c>
     </row>
     <row r="353">
@@ -4887,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.21384636175488</v>
+        <v>-0.931412381379811</v>
       </c>
     </row>
     <row r="354">
@@ -4898,7 +4892,7 @@
         <v>16</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.168123612565608</v>
+        <v>-0.201568346423349</v>
       </c>
     </row>
     <row r="355">
@@ -4920,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.741647601562758</v>
+        <v>-0.954804461191425</v>
       </c>
     </row>
     <row r="357">
@@ -4931,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.503121661758706</v>
       </c>
     </row>
     <row r="358">
@@ -4953,7 +4947,7 @@
         <v>16</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.182361108005747</v>
+        <v>-0.164376376617267</v>
       </c>
     </row>
     <row r="360">
@@ -4964,7 +4958,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.5837751258875</v>
+        <v>-1.93967209592232</v>
       </c>
     </row>
     <row r="361">
@@ -4997,7 +4991,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.163261413624808</v>
+        <v>-0.318692578767641</v>
       </c>
     </row>
     <row r="364">
@@ -5008,7 +5002,7 @@
         <v>16</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.18832890680765</v>
+        <v>-0.197142602352982</v>
       </c>
     </row>
     <row r="365">
@@ -5019,7 +5013,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.139917064889685</v>
       </c>
     </row>
     <row r="366">
@@ -5030,7 +5024,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.592429519650691</v>
+        <v>-0.665474133861463</v>
       </c>
     </row>
     <row r="367">
@@ -5041,7 +5035,7 @@
         <v>16</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.0426459421056937</v>
+        <v>-0.271775577233251</v>
       </c>
     </row>
     <row r="368">
@@ -5052,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.370090118246102</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="369">
@@ -5063,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.772540540799052</v>
       </c>
     </row>
     <row r="370">
@@ -5074,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-1.05054660285815</v>
+        <v>-0.497597194503373</v>
       </c>
     </row>
     <row r="371">
@@ -5096,7 +5090,7 @@
         <v>16</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.256174712567788</v>
+        <v>-0.176744772079266</v>
       </c>
     </row>
     <row r="373">
@@ -5107,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.167931069341569</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="374">
@@ -5129,7 +5123,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>-1.16145162251611</v>
+        <v>-0.0554084534806287</v>
       </c>
     </row>
     <row r="376">
@@ -5140,7 +5134,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.21081009056978</v>
+        <v>-2.39132853338137</v>
       </c>
     </row>
     <row r="377">
@@ -5151,7 +5145,7 @@
         <v>16</v>
       </c>
       <c r="C377" t="n">
-        <v>-0.176235781490602</v>
+        <v>-0.184859363401022</v>
       </c>
     </row>
     <row r="378">
@@ -5173,7 +5167,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.320482911106265</v>
       </c>
     </row>
     <row r="380">
@@ -5184,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.295012571495149</v>
+        <v>-0.261244763733122</v>
       </c>
     </row>
     <row r="381">
@@ -5195,7 +5189,7 @@
         <v>16</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.310173754094631</v>
+        <v>-0.175579608053495</v>
       </c>
     </row>
     <row r="382">
@@ -5206,7 +5200,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.441408036753665</v>
+        <v>-0.426477544633427</v>
       </c>
     </row>
     <row r="383">
@@ -5217,7 +5211,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.37922248459278</v>
       </c>
     </row>
     <row r="384">
@@ -5239,7 +5233,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.171709771666602</v>
       </c>
     </row>
     <row r="386">
@@ -5250,7 +5244,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.410585649067902</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="387">
@@ -5261,7 +5255,7 @@
         <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.282734929489913</v>
       </c>
     </row>
     <row r="388">
@@ -5272,7 +5266,7 @@
         <v>16</v>
       </c>
       <c r="C388" t="n">
-        <v>-0.364173682763723</v>
+        <v>-1.42343811829946</v>
       </c>
     </row>
     <row r="389">
@@ -5283,7 +5277,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.154511635457546</v>
+        <v>-0.113413618900064</v>
       </c>
     </row>
     <row r="390">
@@ -5294,7 +5288,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.294826838398291</v>
+        <v>-48.8194230435308</v>
       </c>
     </row>
     <row r="391">
@@ -5305,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.110617318035621</v>
+        <v>-0.733844322803108</v>
       </c>
     </row>
     <row r="392">
@@ -5316,7 +5310,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.405211355521022</v>
+        <v>-0.231172144610254</v>
       </c>
     </row>
     <row r="393">
@@ -5338,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.270873231115068</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="395">
@@ -5360,7 +5354,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.462663934514485</v>
+        <v>-0.12360167165653</v>
       </c>
     </row>
     <row r="397">
@@ -5371,7 +5365,7 @@
         <v>16</v>
       </c>
       <c r="C397" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.555175761102201</v>
       </c>
     </row>
     <row r="398">
@@ -5382,7 +5376,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-2.07260797427356</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="399">
@@ -5393,7 +5387,7 @@
         <v>16</v>
       </c>
       <c r="C399" t="n">
-        <v>-4.8273020712481</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="400">
@@ -5404,7 +5398,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.216111919398042</v>
+        <v>-0.571941862318825</v>
       </c>
     </row>
     <row r="401">
@@ -5415,7 +5409,7 @@
         <v>16</v>
       </c>
       <c r="C401" t="n">
-        <v>-4.83319730799954</v>
+        <v>-0.153934774686073</v>
       </c>
     </row>
     <row r="402">
@@ -5426,7 +5420,7 @@
         <v>16</v>
       </c>
       <c r="C402" t="n">
-        <v>-0.207355675304156</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="403">
@@ -5437,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="C403" t="n">
-        <v>-16.3697439845133</v>
+        <v>-52.2060264935971</v>
       </c>
     </row>
     <row r="404">
@@ -5448,7 +5442,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.603452459517064</v>
+        <v>-0.591029270274235</v>
       </c>
     </row>
     <row r="405">
@@ -5459,7 +5453,7 @@
         <v>16</v>
       </c>
       <c r="C405" t="n">
-        <v>-0.35441731636225</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="406">
@@ -5470,7 +5464,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.462088310650096</v>
+        <v>-43.9671770758033</v>
       </c>
     </row>
     <row r="407">
@@ -5492,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>0.934000557366618</v>
+        <v>-2.67859866832693</v>
       </c>
     </row>
     <row r="409">
@@ -5514,7 +5508,7 @@
         <v>16</v>
       </c>
       <c r="C410" t="n">
-        <v>-2.15341522103479</v>
+        <v>-0.175053445252255</v>
       </c>
     </row>
     <row r="411">
@@ -5536,7 +5530,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.236615401937902</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="413">
@@ -5558,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.962113073534964</v>
       </c>
     </row>
     <row r="415">
@@ -5591,7 +5585,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.40724044441756</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="418">
@@ -5602,7 +5596,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.186361363879638</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="419">
@@ -5613,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.186532594969391</v>
+        <v>-0.821523922497113</v>
       </c>
     </row>
     <row r="420">
@@ -5624,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>0.307817161699903</v>
+        <v>0.0843966643665254</v>
       </c>
     </row>
     <row r="421">
@@ -5635,7 +5629,7 @@
         <v>16</v>
       </c>
       <c r="C421" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.267787855445245</v>
       </c>
     </row>
     <row r="422">
@@ -5646,7 +5640,7 @@
         <v>16</v>
       </c>
       <c r="C422" t="n">
-        <v>-0.194789840716032</v>
+        <v>-0.1912043006575</v>
       </c>
     </row>
     <row r="423">
@@ -5657,7 +5651,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-4.17188341323606</v>
+        <v>-0.779107591776032</v>
       </c>
     </row>
     <row r="424">
@@ -5668,7 +5662,7 @@
         <v>16</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.215827149443135</v>
+        <v>-0.2829323378455</v>
       </c>
     </row>
     <row r="425">
@@ -5690,7 +5684,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.494482597922055</v>
       </c>
     </row>
     <row r="427">
@@ -5701,7 +5695,7 @@
         <v>16</v>
       </c>
       <c r="C427" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.416553821203771</v>
       </c>
     </row>
     <row r="428">
@@ -5712,7 +5706,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.155665941778625</v>
+        <v>-2.27613960984783</v>
       </c>
     </row>
     <row r="429">
@@ -5723,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.396438902932194</v>
       </c>
     </row>
     <row r="430">
@@ -5778,7 +5772,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.158664741199862</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="435">
@@ -5789,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.593539341344817</v>
+        <v>-1.03402144198624</v>
       </c>
     </row>
     <row r="436">
@@ -5800,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.542951306550263</v>
+        <v>-0.226072720716429</v>
       </c>
     </row>
     <row r="437">
@@ -5811,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>-0.114456754182372</v>
+        <v>0.27590718374001</v>
       </c>
     </row>
     <row r="438">
@@ -5822,7 +5816,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.66088867287531</v>
+        <v>-0.363316256456505</v>
       </c>
     </row>
     <row r="439">
@@ -5833,7 +5827,7 @@
         <v>16</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.47159866728711</v>
+        <v>-0.521454428914219</v>
       </c>
     </row>
     <row r="440">
@@ -5844,7 +5838,7 @@
         <v>16</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.453620672593455</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="441">
@@ -5855,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.823901424662834</v>
       </c>
     </row>
     <row r="442">
@@ -5877,7 +5871,7 @@
         <v>16</v>
       </c>
       <c r="C443" t="n">
-        <v>-0.504285406651365</v>
+        <v>-0.20327608106212</v>
       </c>
     </row>
     <row r="444">
@@ -5888,7 +5882,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.183418929522941</v>
+        <v>-0.146898797045094</v>
       </c>
     </row>
     <row r="445">
@@ -5899,7 +5893,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.590077902708226</v>
       </c>
     </row>
     <row r="446">
@@ -5910,7 +5904,7 @@
         <v>16</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.174498128940231</v>
       </c>
     </row>
     <row r="447">
@@ -5943,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.194057531809135</v>
+        <v>-0.195510054446181</v>
       </c>
     </row>
     <row r="450">
@@ -5954,7 +5948,7 @@
         <v>16</v>
       </c>
       <c r="C450" t="n">
-        <v>-0.205358533371561</v>
+        <v>-0.169221987945422</v>
       </c>
     </row>
     <row r="451">
@@ -5965,7 +5959,7 @@
         <v>16</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.518535559266708</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="452">
@@ -5976,7 +5970,7 @@
         <v>16</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.169412986932168</v>
+        <v>-0.171132565964307</v>
       </c>
     </row>
     <row r="453">
@@ -5987,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>0.132236184028642</v>
+        <v>-0.0612659109965459</v>
       </c>
     </row>
     <row r="454">
@@ -5998,7 +5992,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.173378880722233</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="455">
@@ -6020,7 +6014,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.340712813533538</v>
+        <v>-0.916639944653184</v>
       </c>
     </row>
     <row r="457">
@@ -6031,7 +6025,7 @@
         <v>16</v>
       </c>
       <c r="C457" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.544104867097675</v>
       </c>
     </row>
     <row r="458">
@@ -6042,7 +6036,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.286375402787006</v>
       </c>
     </row>
     <row r="459">
@@ -6075,7 +6069,7 @@
         <v>16</v>
       </c>
       <c r="C461" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.147520667145105</v>
       </c>
     </row>
     <row r="462">
@@ -6086,7 +6080,7 @@
         <v>16</v>
       </c>
       <c r="C462" t="n">
-        <v>-0.174745526115571</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="463">
@@ -6119,7 +6113,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.218946277558657</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="466">
@@ -6130,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.583849514247693</v>
+        <v>-0.202829769614814</v>
       </c>
     </row>
     <row r="467">
@@ -6141,7 +6135,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-0.242879060828071</v>
+        <v>-25.8234787201911</v>
       </c>
     </row>
     <row r="468">
@@ -6152,7 +6146,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.353397588213892</v>
       </c>
     </row>
     <row r="469">
@@ -6174,7 +6168,7 @@
         <v>16</v>
       </c>
       <c r="C470" t="n">
-        <v>-0.209255500729395</v>
+        <v>-0.197748467161511</v>
       </c>
     </row>
     <row r="471">
@@ -6196,7 +6190,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.203267335193506</v>
+        <v>-1.34449039738038</v>
       </c>
     </row>
     <row r="473">
@@ -6207,7 +6201,7 @@
         <v>16</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.493630831340404</v>
+        <v>-44.6666058885716</v>
       </c>
     </row>
     <row r="474">
@@ -6218,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.338971670556</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="475">
@@ -6229,7 +6223,7 @@
         <v>16</v>
       </c>
       <c r="C475" t="n">
-        <v>-0.567682301442421</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="476">
@@ -6240,7 +6234,7 @@
         <v>16</v>
       </c>
       <c r="C476" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.651284379803818</v>
       </c>
     </row>
     <row r="477">
@@ -6251,7 +6245,7 @@
         <v>16</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.316592929031703</v>
+        <v>-0.628291762471602</v>
       </c>
     </row>
     <row r="478">
@@ -6262,7 +6256,7 @@
         <v>16</v>
       </c>
       <c r="C478" t="n">
-        <v>-0.147959183673469</v>
+        <v>-38.0114881702031</v>
       </c>
     </row>
     <row r="479">
@@ -6295,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>-0.101502313111768</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="482">
@@ -6306,7 +6300,7 @@
         <v>16</v>
       </c>
       <c r="C482" t="n">
-        <v>-0.161704924026866</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="483">
@@ -6328,7 +6322,7 @@
         <v>16</v>
       </c>
       <c r="C484" t="n">
-        <v>-0.314974273862211</v>
+        <v>-0.174012121064962</v>
       </c>
     </row>
     <row r="485">
@@ -6339,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.0953704696573865</v>
+        <v>-18.1586684429267</v>
       </c>
     </row>
     <row r="486">
@@ -6350,7 +6344,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.297040704063465</v>
+        <v>-0.4526657896592</v>
       </c>
     </row>
     <row r="487">
@@ -6361,7 +6355,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.159658381557579</v>
       </c>
     </row>
     <row r="488">
@@ -6372,7 +6366,7 @@
         <v>16</v>
       </c>
       <c r="C488" t="n">
-        <v>-0.282265547481131</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="489">
@@ -6394,7 +6388,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-0.250620168578864</v>
+        <v>-0.137160420106446</v>
       </c>
     </row>
     <row r="491">
@@ -6405,7 +6399,7 @@
         <v>16</v>
       </c>
       <c r="C491" t="n">
-        <v>-2.15345145039747</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="492">
@@ -6416,7 +6410,7 @@
         <v>16</v>
       </c>
       <c r="C492" t="n">
-        <v>-0.709060412850152</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="493">
@@ -6438,7 +6432,7 @@
         <v>16</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.2026306638623</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="495">
@@ -6449,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.312455183716198</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="496">
@@ -6460,7 +6454,7 @@
         <v>16</v>
       </c>
       <c r="C496" t="n">
-        <v>-4.73739501794906</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="497">
@@ -6471,7 +6465,7 @@
         <v>16</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.304138667587833</v>
       </c>
     </row>
     <row r="498">
@@ -6493,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.199743536934295</v>
+        <v>-0.658673272234506</v>
       </c>
     </row>
     <row r="500">
@@ -6504,7 +6498,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.732599121499665</v>
+        <v>-27.3618663802354</v>
       </c>
     </row>
     <row r="501">
@@ -6526,7 +6520,7 @@
         <v>16</v>
       </c>
       <c r="C502" t="n">
-        <v>-5.13689582633524</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="503">
@@ -6537,7 +6531,7 @@
         <v>16</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.231420392218032</v>
+        <v>-0.375354702956998</v>
       </c>
     </row>
     <row r="504">
@@ -6570,7 +6564,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>-3.99448372072434</v>
+        <v>-0.289737899270482</v>
       </c>
     </row>
     <row r="507">
@@ -6581,7 +6575,7 @@
         <v>16</v>
       </c>
       <c r="C507" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.393367582170485</v>
       </c>
     </row>
     <row r="508">
@@ -6592,7 +6586,7 @@
         <v>16</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.706753833378362</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="509">
@@ -6603,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.363371993605954</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="510">
@@ -6625,7 +6619,7 @@
         <v>16</v>
       </c>
       <c r="C511" t="n">
-        <v>-0.225836862230896</v>
+        <v>-0.270313432894403</v>
       </c>
     </row>
     <row r="512">
@@ -6647,7 +6641,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.587159135842928</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="514">
@@ -6669,7 +6663,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.287968877530255</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="516">
@@ -6691,7 +6685,7 @@
         <v>16</v>
       </c>
       <c r="C517" t="n">
-        <v>-1.58977372141923</v>
+        <v>-0.27364619435335</v>
       </c>
     </row>
     <row r="518">
@@ -6746,7 +6740,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.272147035006948</v>
+        <v>-0.243369365945064</v>
       </c>
     </row>
     <row r="523">
@@ -6768,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.352612330880468</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="525">
@@ -6779,7 +6773,7 @@
         <v>16</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.196002878608728</v>
+        <v>-0.23065862277372</v>
       </c>
     </row>
     <row r="526">
@@ -6790,7 +6784,7 @@
         <v>16</v>
       </c>
       <c r="C526" t="n">
-        <v>-0.339896092809078</v>
+        <v>-0.363792101691862</v>
       </c>
     </row>
     <row r="527">
@@ -6801,7 +6795,7 @@
         <v>16</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.179751696538182</v>
+        <v>-0.189135045858233</v>
       </c>
     </row>
     <row r="528">
@@ -6812,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.304675544378246</v>
+        <v>-0.220656104587075</v>
       </c>
     </row>
     <row r="529">
@@ -6845,7 +6839,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.190829719456391</v>
+        <v>-0.448908030028424</v>
       </c>
     </row>
     <row r="532">
@@ -6856,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-1.61436735875149</v>
+        <v>-2.11050455050917</v>
       </c>
     </row>
     <row r="533">
@@ -6878,7 +6872,7 @@
         <v>16</v>
       </c>
       <c r="C534" t="n">
-        <v>-11.7763665312446</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="535">
@@ -6889,7 +6883,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.531752612499868</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="536">
@@ -6900,7 +6894,7 @@
         <v>16</v>
       </c>
       <c r="C536" t="n">
-        <v>0.419014637364232</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="537">
@@ -6911,7 +6905,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.178399253166236</v>
       </c>
     </row>
     <row r="538">
@@ -6922,7 +6916,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>0.379129778187953</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="539">
@@ -6933,7 +6927,7 @@
         <v>16</v>
       </c>
       <c r="C539" t="n">
-        <v>-0.23239795013993</v>
+        <v>-0.259437869181181</v>
       </c>
     </row>
     <row r="540">
@@ -6966,7 +6960,7 @@
         <v>16</v>
       </c>
       <c r="C542" t="n">
-        <v>-0.385364589434513</v>
+        <v>-0.226146242823601</v>
       </c>
     </row>
     <row r="543">
@@ -6977,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.155382589155354</v>
+        <v>-0.370474096641526</v>
       </c>
     </row>
     <row r="544">
@@ -7010,7 +7004,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.469372079035781</v>
+        <v>-0.508006933547724</v>
       </c>
     </row>
     <row r="547">
@@ -7021,7 +7015,7 @@
         <v>16</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.294635219421352</v>
+        <v>-1.21462710062927</v>
       </c>
     </row>
     <row r="548">
@@ -7032,7 +7026,7 @@
         <v>16</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.190609184519432</v>
       </c>
     </row>
     <row r="549">
@@ -7043,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.406026290250107</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="550">
@@ -7065,7 +7059,7 @@
         <v>16</v>
       </c>
       <c r="C551" t="n">
-        <v>-2.1578459784931</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="552">
@@ -7076,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.237131469219077</v>
+        <v>-0.229593860909217</v>
       </c>
     </row>
     <row r="553">
@@ -7087,7 +7081,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.419869028532367</v>
+        <v>-0.422990625912653</v>
       </c>
     </row>
     <row r="554">
@@ -7098,7 +7092,7 @@
         <v>16</v>
       </c>
       <c r="C554" t="n">
-        <v>-2.58095759225644</v>
+        <v>-0.195173408518308</v>
       </c>
     </row>
     <row r="555">
@@ -7109,7 +7103,7 @@
         <v>16</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.808832909955099</v>
       </c>
     </row>
     <row r="556">
@@ -7120,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-4.10081798685246</v>
+        <v>-0.902402485077149</v>
       </c>
     </row>
     <row r="557">
@@ -7131,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.587217578057548</v>
+        <v>-0.354295019202039</v>
       </c>
     </row>
     <row r="558">
@@ -7142,7 +7136,7 @@
         <v>16</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.241983656371724</v>
       </c>
     </row>
     <row r="559">
@@ -7153,7 +7147,7 @@
         <v>16</v>
       </c>
       <c r="C559" t="n">
-        <v>-0.264662749080824</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="560">
@@ -7164,7 +7158,7 @@
         <v>16</v>
       </c>
       <c r="C560" t="n">
-        <v>-1.53331050724725</v>
+        <v>-0.776944273555134</v>
       </c>
     </row>
     <row r="561">
@@ -7197,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.153717641864589</v>
+        <v>-0.236758423930886</v>
       </c>
     </row>
     <row r="564">
@@ -7208,7 +7202,7 @@
         <v>16</v>
       </c>
       <c r="C564" t="n">
-        <v>-0.491325237094258</v>
+        <v>-0.188405782462958</v>
       </c>
     </row>
     <row r="565">
@@ -7219,7 +7213,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.261979167780356</v>
       </c>
     </row>
     <row r="566">
@@ -7241,7 +7235,7 @@
         <v>16</v>
       </c>
       <c r="C567" t="n">
-        <v>-0.184805642466353</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="568">
@@ -7263,7 +7257,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.118955993830625</v>
+        <v>-0.484691598184658</v>
       </c>
     </row>
     <row r="570">
@@ -7274,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.627045213323542</v>
+        <v>-0.570189880940658</v>
       </c>
     </row>
     <row r="571">
@@ -7296,7 +7290,7 @@
         <v>16</v>
       </c>
       <c r="C572" t="n">
-        <v>-0.349968517357699</v>
+        <v>-0.873273337272074</v>
       </c>
     </row>
     <row r="573">
@@ -7307,7 +7301,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.446176726210615</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="574">
@@ -7329,7 +7323,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.233098598424434</v>
+        <v>-0.481347153461382</v>
       </c>
     </row>
     <row r="576">
@@ -7340,7 +7334,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.233383110708365</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="577">
@@ -7373,7 +7367,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.545673010761577</v>
       </c>
     </row>
     <row r="580">
@@ -7384,7 +7378,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.410446662743998</v>
+        <v>-0.171584355853266</v>
       </c>
     </row>
     <row r="581">
@@ -7395,7 +7389,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.194865976915105</v>
+        <v>-0.152528663578595</v>
       </c>
     </row>
     <row r="582">
@@ -7406,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>0.0367510305740354</v>
+        <v>-0.338410845729955</v>
       </c>
     </row>
     <row r="583">
@@ -7417,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.193403077031372</v>
+        <v>-0.253044666135515</v>
       </c>
     </row>
     <row r="584">
@@ -7439,7 +7433,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.140185978390792</v>
       </c>
     </row>
     <row r="586">
@@ -7450,7 +7444,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.412861758746719</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="587">
@@ -7461,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.539297961850035</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="588">
@@ -7472,7 +7466,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.258686131466016</v>
+        <v>-0.247990494641435</v>
       </c>
     </row>
     <row r="589">
@@ -7483,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.12592120660061</v>
+        <v>-0.226232094006351</v>
       </c>
     </row>
     <row r="590">
@@ -7494,7 +7488,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.197774410651235</v>
+        <v>-0.276578461714026</v>
       </c>
     </row>
     <row r="591">
@@ -7505,7 +7499,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.246735870296588</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="592">
@@ -7516,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.270590106837575</v>
+        <v>-0.219181110611347</v>
       </c>
     </row>
     <row r="593">
@@ -7538,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.606623677792059</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="595">
@@ -7560,7 +7554,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.290347564865424</v>
+        <v>-0.737775271917783</v>
       </c>
     </row>
     <row r="597">
@@ -7571,7 +7565,7 @@
         <v>16</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.474470725790585</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="598">
@@ -7615,7 +7609,7 @@
         <v>16</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.195005012515684</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="602">
@@ -7626,7 +7620,7 @@
         <v>16</v>
       </c>
       <c r="C602" t="n">
-        <v>-0.147959183673469</v>
+        <v>-98.575898216362</v>
       </c>
     </row>
     <row r="603">
@@ -7659,7 +7653,7 @@
         <v>16</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.23560812993043</v>
+        <v>-95.9209690174005</v>
       </c>
     </row>
     <row r="606">
@@ -7670,7 +7664,7 @@
         <v>16</v>
       </c>
       <c r="C606" t="n">
-        <v>-0.00481930332331548</v>
+        <v>-0.23518666828686</v>
       </c>
     </row>
     <row r="607">
@@ -7681,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-1.01927456483006</v>
+        <v>-1.30987475606685</v>
       </c>
     </row>
     <row r="608">
@@ -7703,7 +7697,7 @@
         <v>16</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.171515935200278</v>
+        <v>-0.86203176645143</v>
       </c>
     </row>
     <row r="610">
@@ -7714,7 +7708,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.249886747895821</v>
+        <v>-0.32046689715815</v>
       </c>
     </row>
     <row r="611">
@@ -7725,7 +7719,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-1.24543839965351</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="612">
@@ -7747,7 +7741,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>0.655106840701496</v>
+        <v>-0.237541105668369</v>
       </c>
     </row>
     <row r="614">
@@ -7780,7 +7774,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>0.48448099655336</v>
+        <v>-0.131129010770451</v>
       </c>
     </row>
     <row r="617">
@@ -7802,7 +7796,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.0393025236424873</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="619">
@@ -7813,7 +7807,7 @@
         <v>16</v>
       </c>
       <c r="C619" t="n">
-        <v>-1.43674610014542</v>
+        <v>-0.709258693130247</v>
       </c>
     </row>
     <row r="620">
@@ -7824,7 +7818,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.140916109370473</v>
+        <v>-0.13909596763245</v>
       </c>
     </row>
     <row r="621">
@@ -7835,7 +7829,7 @@
         <v>16</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.205862773653098</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="622">
@@ -7846,7 +7840,7 @@
         <v>16</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.698341110482064</v>
+        <v>-0.781723337655355</v>
       </c>
     </row>
     <row r="623">
@@ -7868,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.304476123627687</v>
+        <v>-0.428750697500166</v>
       </c>
     </row>
     <row r="625">
@@ -7879,7 +7873,7 @@
         <v>16</v>
       </c>
       <c r="C625" t="n">
-        <v>-0.440319626385716</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="626">
@@ -7890,7 +7884,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.671597280412915</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="627">
@@ -7901,7 +7895,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.25796779857574</v>
       </c>
     </row>
     <row r="628">
@@ -7912,7 +7906,7 @@
         <v>16</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.174889786618518</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="629">
@@ -7923,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.58132879646055</v>
+        <v>-0.153105478162797</v>
       </c>
     </row>
     <row r="630">
@@ -7934,7 +7928,7 @@
         <v>16</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.362001659614655</v>
+        <v>-0.952000927825865</v>
       </c>
     </row>
     <row r="631">
@@ -7945,7 +7939,7 @@
         <v>16</v>
       </c>
       <c r="C631" t="n">
-        <v>-0.153779703245041</v>
+        <v>-0.206908430090617</v>
       </c>
     </row>
     <row r="632">
@@ -7956,7 +7950,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-1.72391369565758</v>
+        <v>-0.407787292830646</v>
       </c>
     </row>
     <row r="633">
@@ -7967,7 +7961,7 @@
         <v>16</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.369465341309676</v>
+        <v>-0.148579977523356</v>
       </c>
     </row>
     <row r="634">
@@ -7978,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.142502813234236</v>
       </c>
     </row>
     <row r="635">
@@ -7989,7 +7983,7 @@
         <v>16</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.338821046346047</v>
+        <v>-0.151499938531054</v>
       </c>
     </row>
     <row r="636">
@@ -8000,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.296608091532595</v>
       </c>
     </row>
     <row r="637">
@@ -8011,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.162340050861328</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="638">
@@ -8033,7 +8027,7 @@
         <v>16</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.248668219246391</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="640">
@@ -8044,7 +8038,7 @@
         <v>16</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.630060132969065</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="641">
@@ -8055,7 +8049,7 @@
         <v>16</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.335517551949985</v>
+        <v>-0.630430394527168</v>
       </c>
     </row>
     <row r="642">
@@ -8066,7 +8060,7 @@
         <v>16</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.147959183673469</v>
+        <v>-19.5753312518679</v>
       </c>
     </row>
     <row r="643">
@@ -8077,7 +8071,7 @@
         <v>16</v>
       </c>
       <c r="C643" t="n">
-        <v>-0.376128493272964</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="644">
@@ -8088,7 +8082,7 @@
         <v>16</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.528942925957344</v>
+        <v>-0.493992831268378</v>
       </c>
     </row>
     <row r="645">
@@ -8099,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.452423424584173</v>
+        <v>-0.558359232374234</v>
       </c>
     </row>
     <row r="646">
@@ -8110,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.0741938979093821</v>
+        <v>-0.108974258551762</v>
       </c>
     </row>
     <row r="647">
@@ -8121,7 +8115,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.406196117722853</v>
+        <v>0.0732074374675006</v>
       </c>
     </row>
     <row r="648">
@@ -8132,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.169608324794271</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="649">
@@ -8143,7 +8137,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>-1.02469122583162</v>
+        <v>-0.211975892041614</v>
       </c>
     </row>
     <row r="650">
@@ -8154,7 +8148,7 @@
         <v>16</v>
       </c>
       <c r="C650" t="n">
-        <v>-3.05587771393176</v>
+        <v>-0.264902942164083</v>
       </c>
     </row>
     <row r="651">
@@ -8165,7 +8159,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.357484225352249</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="652">
@@ -8176,7 +8170,7 @@
         <v>16</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.228517431205046</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="653">
@@ -8187,7 +8181,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.244810207567365</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="654">
@@ -8209,7 +8203,7 @@
         <v>16</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.231921688673106</v>
+        <v>-0.495633334931656</v>
       </c>
     </row>
     <row r="656">
@@ -8231,7 +8225,7 @@
         <v>16</v>
       </c>
       <c r="C657" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.260804892063331</v>
       </c>
     </row>
     <row r="658">
@@ -8253,7 +8247,7 @@
         <v>16</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.18943451110906</v>
+        <v>-0.212511802333737</v>
       </c>
     </row>
     <row r="660">
@@ -8264,7 +8258,7 @@
         <v>16</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.451033101219561</v>
       </c>
     </row>
     <row r="661">
@@ -8275,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.426045963618922</v>
+        <v>-0.352266010558294</v>
       </c>
     </row>
     <row r="662">
@@ -8286,7 +8280,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.202901748006499</v>
+        <v>-0.285395461035145</v>
       </c>
     </row>
     <row r="663">
@@ -8297,7 +8291,7 @@
         <v>16</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.279060986996514</v>
       </c>
     </row>
     <row r="664">
@@ -8308,7 +8302,7 @@
         <v>16</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.72836434085371</v>
+        <v>-5.20119771424057</v>
       </c>
     </row>
     <row r="665">
@@ -8319,7 +8313,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.632913204480409</v>
+        <v>-59.7632989118975</v>
       </c>
     </row>
     <row r="666">
@@ -8330,7 +8324,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.194601661992654</v>
       </c>
     </row>
     <row r="667">
@@ -8341,7 +8335,7 @@
         <v>16</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.166696817624968</v>
       </c>
     </row>
     <row r="668">
@@ -8363,7 +8357,7 @@
         <v>16</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.51788475108653</v>
       </c>
     </row>
     <row r="670">
@@ -8374,7 +8368,7 @@
         <v>16</v>
       </c>
       <c r="C670" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.541794726679822</v>
       </c>
     </row>
     <row r="671">
@@ -8396,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-1.23020730930663</v>
+        <v>-2.74195149091984</v>
       </c>
     </row>
     <row r="673">
@@ -8407,7 +8401,7 @@
         <v>16</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.146566625768718</v>
+        <v>-0.273270475975272</v>
       </c>
     </row>
     <row r="674">
@@ -8418,7 +8412,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.23489886663282</v>
       </c>
     </row>
     <row r="675">
@@ -8440,7 +8434,7 @@
         <v>16</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.465574633327953</v>
+        <v>-0.78272661070357</v>
       </c>
     </row>
     <row r="677">
@@ -8451,7 +8445,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.309374975567351</v>
+        <v>-0.139950113547694</v>
       </c>
     </row>
     <row r="678">
@@ -8462,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.0765877053031327</v>
+        <v>-0.10451130539516</v>
       </c>
     </row>
     <row r="679">
@@ -8473,7 +8467,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.512158602264538</v>
+        <v>-0.525326451598013</v>
       </c>
     </row>
     <row r="680">
@@ -8484,7 +8478,7 @@
         <v>16</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.402958260602002</v>
+        <v>-0.211470284916613</v>
       </c>
     </row>
     <row r="681">
@@ -8495,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>0.0311860905868513</v>
+        <v>-0.280725589585896</v>
       </c>
     </row>
     <row r="682">
@@ -8517,7 +8511,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.257703468363362</v>
       </c>
     </row>
     <row r="684">
@@ -8528,7 +8522,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.417554807813765</v>
+        <v>-0.341968743859106</v>
       </c>
     </row>
     <row r="685">
@@ -8539,7 +8533,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.54378032807357</v>
+        <v>-0.170900300882182</v>
       </c>
     </row>
     <row r="686">
@@ -8572,7 +8566,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.49080723766179</v>
+        <v>-0.170083466899086</v>
       </c>
     </row>
     <row r="689">
@@ -8616,7 +8610,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.80741143391537</v>
+        <v>-6.33480217829582</v>
       </c>
     </row>
     <row r="693">
@@ -8627,7 +8621,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.14084723916202</v>
+        <v>-0.232251865770815</v>
       </c>
     </row>
     <row r="694">
@@ -8649,7 +8643,7 @@
         <v>16</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.509014900192053</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="696">
@@ -8660,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.192889435961004</v>
+        <v>-0.188625421124009</v>
       </c>
     </row>
     <row r="697">
@@ -8682,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.14795918367347</v>
+        <v>0.265999824992175</v>
       </c>
     </row>
     <row r="699">
@@ -8693,7 +8687,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-2.29511898858754</v>
+        <v>0.000509203776705602</v>
       </c>
     </row>
     <row r="700">
@@ -8704,7 +8698,7 @@
         <v>16</v>
       </c>
       <c r="C700" t="n">
-        <v>-1.15547873740157</v>
+        <v>-0.346112964789296</v>
       </c>
     </row>
     <row r="701">
@@ -8726,7 +8720,7 @@
         <v>16</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.00421359890821926</v>
       </c>
     </row>
     <row r="703">
@@ -8737,7 +8731,7 @@
         <v>16</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.136810101514754</v>
       </c>
     </row>
     <row r="704">
@@ -8759,7 +8753,7 @@
         <v>16</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.248238877078323</v>
+        <v>-0.487465665331299</v>
       </c>
     </row>
     <row r="706">
@@ -8770,7 +8764,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.118182928508737</v>
+        <v>-0.497056478386922</v>
       </c>
     </row>
     <row r="707">
@@ -8781,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.628202405630208</v>
+        <v>-0.180195106844221</v>
       </c>
     </row>
     <row r="708">
@@ -8792,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.202136832272097</v>
+        <v>-0.19302330752435</v>
       </c>
     </row>
     <row r="709">
@@ -8814,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.297672210433835</v>
+        <v>-0.200036018652035</v>
       </c>
     </row>
     <row r="711">
@@ -8825,7 +8819,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-5.39047403223404</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="712">
@@ -8858,7 +8852,7 @@
         <v>16</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.388417911989002</v>
+        <v>-0.205965144188033</v>
       </c>
     </row>
     <row r="715">
@@ -8869,7 +8863,7 @@
         <v>16</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.194286837058362</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="716">
@@ -8880,7 +8874,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.940062030289595</v>
+        <v>-0.201181711494493</v>
       </c>
     </row>
     <row r="717">
@@ -8902,7 +8896,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.155248435533025</v>
+        <v>-0.323390707837154</v>
       </c>
     </row>
     <row r="719">
@@ -8913,7 +8907,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.209765035506242</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="720">
@@ -8935,7 +8929,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>-2.53838476122508</v>
+        <v>-3.05277643265345</v>
       </c>
     </row>
     <row r="722">
@@ -8946,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.345747082175704</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="723">
@@ -8957,7 +8951,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.467532597716148</v>
+        <v>-0.242432058479382</v>
       </c>
     </row>
     <row r="724">
@@ -8968,7 +8962,7 @@
         <v>16</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.359365437196665</v>
       </c>
     </row>
     <row r="725">
@@ -8979,7 +8973,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-1.37600560136689</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="726">
@@ -8990,7 +8984,7 @@
         <v>16</v>
       </c>
       <c r="C726" t="n">
-        <v>0.50307217726984</v>
+        <v>0.662344770522718</v>
       </c>
     </row>
     <row r="727">
@@ -9001,7 +8995,7 @@
         <v>16</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.147959183673469</v>
+        <v>-6.33282453306477</v>
       </c>
     </row>
     <row r="728">
@@ -9023,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.189656999998329</v>
+        <v>-0.284938394372059</v>
       </c>
     </row>
     <row r="730">
@@ -9067,7 +9061,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.21362409968254</v>
       </c>
     </row>
     <row r="734">
@@ -9122,7 +9116,7 @@
         <v>16</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.48052362390729</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="739">
@@ -9133,7 +9127,7 @@
         <v>16</v>
       </c>
       <c r="C739" t="n">
-        <v>0.0527339621082173</v>
+        <v>-76.0699405113238</v>
       </c>
     </row>
     <row r="740">
@@ -9144,7 +9138,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.3900287730856</v>
+        <v>-0.431571969574784</v>
       </c>
     </row>
     <row r="741">
@@ -9155,7 +9149,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.290530441505827</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="742">
@@ -9166,7 +9160,7 @@
         <v>16</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.315961154341392</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="743">
@@ -9177,7 +9171,7 @@
         <v>16</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.403695531220088</v>
+        <v>-0.891681537718959</v>
       </c>
     </row>
     <row r="744">
@@ -9188,7 +9182,7 @@
         <v>16</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.198343298608365</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="745">
@@ -9243,7 +9237,7 @@
         <v>16</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.163900664956332</v>
+        <v>-0.253543510006446</v>
       </c>
     </row>
     <row r="750">
@@ -9265,7 +9259,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.193219398900162</v>
+        <v>-0.168034897680697</v>
       </c>
     </row>
     <row r="752">
@@ -9298,7 +9292,7 @@
         <v>16</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.11919370566573</v>
       </c>
     </row>
     <row r="755">
@@ -9309,7 +9303,7 @@
         <v>16</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.161005463953562</v>
+        <v>-0.24315330432438</v>
       </c>
     </row>
     <row r="756">
@@ -9342,7 +9336,7 @@
         <v>16</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.20417574724267</v>
+        <v>-0.257820647140053</v>
       </c>
     </row>
     <row r="759">
@@ -9353,7 +9347,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.224327679999297</v>
+        <v>-3.83633981022593</v>
       </c>
     </row>
     <row r="760">
@@ -9364,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.185792616379253</v>
       </c>
     </row>
     <row r="761">
@@ -9375,7 +9369,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.0804641643740283</v>
+        <v>-0.00633527529819844</v>
       </c>
     </row>
     <row r="762">
@@ -9386,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.180156291529963</v>
+        <v>-0.137725017226274</v>
       </c>
     </row>
     <row r="763">
@@ -9397,7 +9391,7 @@
         <v>16</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.350941510973376</v>
+        <v>-0.331807383446</v>
       </c>
     </row>
     <row r="764">
@@ -9408,7 +9402,7 @@
         <v>16</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.513029813871616</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="765">
@@ -9419,7 +9413,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.373957987227454</v>
+        <v>-0.472390779753528</v>
       </c>
     </row>
     <row r="766">
@@ -9430,7 +9424,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.736824314234077</v>
+        <v>-0.538303327313363</v>
       </c>
     </row>
     <row r="767">
@@ -9474,7 +9468,7 @@
         <v>16</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.498508246618541</v>
+        <v>-0.286287775164277</v>
       </c>
     </row>
     <row r="771">
@@ -9485,7 +9479,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.355469139097005</v>
+        <v>-0.30737051350383</v>
       </c>
     </row>
     <row r="772">
@@ -9529,7 +9523,7 @@
         <v>16</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.566910662270086</v>
       </c>
     </row>
     <row r="776">
@@ -9540,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.236007098603231</v>
+        <v>-0.252777614202414</v>
       </c>
     </row>
     <row r="777">
@@ -9551,7 +9545,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.741743671698343</v>
+        <v>-46.3706505990797</v>
       </c>
     </row>
     <row r="778">
@@ -9562,7 +9556,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.161570147595439</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="779">
@@ -9584,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.183371985882394</v>
+        <v>-0.413655002410416</v>
       </c>
     </row>
     <row r="781">
@@ -9595,7 +9589,7 @@
         <v>16</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.147959183673469</v>
+        <v>-10.0783880156385</v>
       </c>
     </row>
     <row r="782">
@@ -9617,7 +9611,7 @@
         <v>16</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.345985766308313</v>
+        <v>-0.385998805698184</v>
       </c>
     </row>
     <row r="784">
@@ -9628,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.184703035815178</v>
+        <v>-0.146076401114273</v>
       </c>
     </row>
     <row r="785">
@@ -9639,7 +9633,7 @@
         <v>16</v>
       </c>
       <c r="C785" t="n">
-        <v>-2.43939221350741</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="786">
@@ -9650,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.253937312924269</v>
+        <v>-0.326576024374477</v>
       </c>
     </row>
     <row r="787">
@@ -9672,7 +9666,7 @@
         <v>16</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.199288810492495</v>
       </c>
     </row>
     <row r="789">
@@ -9683,7 +9677,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.362353427127068</v>
       </c>
     </row>
     <row r="790">
@@ -9705,7 +9699,7 @@
         <v>16</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.42389723849862</v>
       </c>
     </row>
     <row r="792">
@@ -9716,7 +9710,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.472943040602692</v>
+        <v>-22.5693022542118</v>
       </c>
     </row>
     <row r="793">
@@ -9727,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>0.3257319984742</v>
+        <v>-0.529881814261252</v>
       </c>
     </row>
     <row r="794">
@@ -9738,7 +9732,7 @@
         <v>16</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.327943073717127</v>
+        <v>-0.350283462249019</v>
       </c>
     </row>
     <row r="795">
@@ -9749,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.297954049440254</v>
+        <v>-0.233080841325375</v>
       </c>
     </row>
     <row r="796">
@@ -9760,7 +9754,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.421721875363729</v>
+        <v>-8.95232270572048</v>
       </c>
     </row>
     <row r="797">
@@ -9771,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.219958586644698</v>
+        <v>-0.16772994068971</v>
       </c>
     </row>
     <row r="798">
@@ -9782,7 +9776,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.214432298064475</v>
+        <v>-0.232912735796991</v>
       </c>
     </row>
     <row r="799">
@@ -9793,7 +9787,7 @@
         <v>16</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.306101419165327</v>
+        <v>-0.337490295687062</v>
       </c>
     </row>
     <row r="800">
@@ -9815,7 +9809,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.14795918367347</v>
+        <v>-4.5815269775904</v>
       </c>
     </row>
     <row r="802">
@@ -9826,7 +9820,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.732976034001624</v>
+        <v>-0.559726946839713</v>
       </c>
     </row>
     <row r="803">
@@ -9837,7 +9831,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-9.93140907970384</v>
+        <v>-0.569776266431599</v>
       </c>
     </row>
     <row r="804">
@@ -9848,7 +9842,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.35285346868666</v>
       </c>
     </row>
     <row r="805">
@@ -9859,7 +9853,7 @@
         <v>16</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.229973656639624</v>
+        <v>-0.212824113952821</v>
       </c>
     </row>
     <row r="806">
@@ -9870,7 +9864,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.165138347222896</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="807">
@@ -9881,7 +9875,7 @@
         <v>16</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.147959183673469</v>
+        <v>-5.91833062767415</v>
       </c>
     </row>
     <row r="808">
@@ -9892,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.132534817826295</v>
+        <v>-5.37145683916632</v>
       </c>
     </row>
     <row r="809">
@@ -9903,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.24871501665789</v>
+        <v>-0.270025167633532</v>
       </c>
     </row>
     <row r="810">
@@ -9925,7 +9919,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-36.2326293094007</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="812">
@@ -9936,7 +9930,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.479045400332522</v>
       </c>
     </row>
     <row r="813">
@@ -9947,7 +9941,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>-1.81285159459301</v>
+        <v>-0.321250107124054</v>
       </c>
     </row>
     <row r="814">
@@ -9958,7 +9952,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.427937459334622</v>
+        <v>-0.316127910273586</v>
       </c>
     </row>
     <row r="815">
@@ -9969,7 +9963,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.539609448165241</v>
+        <v>-0.331940393019039</v>
       </c>
     </row>
     <row r="816">
@@ -9980,7 +9974,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.170309222740313</v>
+        <v>0.00341370805934249</v>
       </c>
     </row>
     <row r="817">
@@ -9991,7 +9985,7 @@
         <v>16</v>
       </c>
       <c r="C817" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.241631844453752</v>
       </c>
     </row>
     <row r="818">
@@ -10002,7 +9996,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.32553124618631</v>
       </c>
     </row>
     <row r="819">
@@ -10013,7 +10007,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.297991736934098</v>
+        <v>-0.279256051727478</v>
       </c>
     </row>
     <row r="820">
@@ -10024,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.196877054218216</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="821">
@@ -10035,7 +10029,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.472572351026237</v>
+        <v>-0.26507838509645</v>
       </c>
     </row>
     <row r="822">
@@ -10068,7 +10062,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.315351590225758</v>
+        <v>-0.228881423917063</v>
       </c>
     </row>
     <row r="825">
@@ -10079,7 +10073,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.359790676203892</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="826">
@@ -10090,7 +10084,7 @@
         <v>16</v>
       </c>
       <c r="C826" t="n">
-        <v>0.147863104271444</v>
+        <v>-0.174304151801284</v>
       </c>
     </row>
     <row r="827">
@@ -10112,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.171457446320059</v>
       </c>
     </row>
     <row r="829">
@@ -10123,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.118095186216861</v>
+        <v>-0.0142704872935884</v>
       </c>
     </row>
     <row r="830">
@@ -10134,7 +10128,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.207207361307982</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="831">
@@ -10145,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.160412851498223</v>
       </c>
     </row>
     <row r="832">
@@ -10156,7 +10150,7 @@
         <v>16</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.319102277949986</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="833">
@@ -10167,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.134225964376274</v>
+        <v>-0.184617170106425</v>
       </c>
     </row>
     <row r="834">
@@ -10178,7 +10172,7 @@
         <v>16</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.224555952492315</v>
+        <v>-0.218441213661553</v>
       </c>
     </row>
     <row r="835">
@@ -10189,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.281716466399209</v>
+        <v>-0.26923402120236</v>
       </c>
     </row>
     <row r="836">
@@ -10200,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.647839291410779</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="837">
@@ -10211,7 +10205,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.174106828521518</v>
+        <v>-0.340744143077762</v>
       </c>
     </row>
     <row r="838">
@@ -10222,7 +10216,7 @@
         <v>16</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.797334605817347</v>
+        <v>-0.23439691409302</v>
       </c>
     </row>
     <row r="839">
@@ -10233,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.224815020392645</v>
       </c>
     </row>
     <row r="840">
@@ -10244,7 +10238,7 @@
         <v>16</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.23935771466976</v>
+        <v>-0.196046014582232</v>
       </c>
     </row>
     <row r="841">
@@ -10255,7 +10249,7 @@
         <v>16</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.14718393168978</v>
       </c>
     </row>
     <row r="842">
@@ -10266,7 +10260,7 @@
         <v>16</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.371295510536946</v>
+        <v>-0.701673199008327</v>
       </c>
     </row>
     <row r="843">
@@ -10277,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>0.365830563769353</v>
+        <v>-0.157207555373571</v>
       </c>
     </row>
     <row r="844">
@@ -10288,7 +10282,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-2.21558841325247</v>
+        <v>-2.17267740241339</v>
       </c>
     </row>
     <row r="845">
@@ -10299,7 +10293,7 @@
         <v>16</v>
       </c>
       <c r="C845" t="n">
-        <v>0.0802645557080733</v>
+        <v>-0.265835158668551</v>
       </c>
     </row>
     <row r="846">
@@ -10310,7 +10304,7 @@
         <v>16</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.199950332427348</v>
       </c>
     </row>
     <row r="847">
@@ -10321,7 +10315,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.593868008578498</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="848">
@@ -10332,7 +10326,7 @@
         <v>16</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.354344653726197</v>
+        <v>-0.264805567846291</v>
       </c>
     </row>
     <row r="849">
@@ -10343,7 +10337,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.172609323444319</v>
       </c>
     </row>
     <row r="850">
@@ -10354,7 +10348,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.751885434385243</v>
+        <v>-0.481995895384037</v>
       </c>
     </row>
     <row r="851">
@@ -10365,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.292100146990496</v>
+        <v>-0.259902526107552</v>
       </c>
     </row>
     <row r="852">
@@ -10376,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-2.117710755596</v>
+        <v>-2.15217754526419</v>
       </c>
     </row>
     <row r="853">
@@ -10387,7 +10381,7 @@
         <v>16</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.176850320735473</v>
+        <v>-0.214395810232679</v>
       </c>
     </row>
     <row r="854">
@@ -10398,7 +10392,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.204875725181578</v>
       </c>
     </row>
     <row r="855">
@@ -10420,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.262071958408195</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="857">
@@ -10431,7 +10425,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.10639247607458</v>
+        <v>-0.171974314362601</v>
       </c>
     </row>
     <row r="858">
@@ -10442,7 +10436,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.294016120187268</v>
+        <v>-0.163607388570952</v>
       </c>
     </row>
     <row r="859">
@@ -10464,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.490900506781215</v>
+        <v>-0.339999222730391</v>
       </c>
     </row>
     <row r="861">
@@ -10475,7 +10469,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-16.2339360005078</v>
+        <v>-1.23472631973777</v>
       </c>
     </row>
     <row r="862">
@@ -10486,7 +10480,7 @@
         <v>16</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.295423522581299</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="863">
@@ -10508,7 +10502,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.823549801062329</v>
       </c>
     </row>
     <row r="865">
@@ -10519,7 +10513,7 @@
         <v>16</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.426808105951324</v>
+        <v>-0.333457873611121</v>
       </c>
     </row>
     <row r="866">
@@ -10530,7 +10524,7 @@
         <v>16</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.238932431828088</v>
+        <v>-0.180497370639941</v>
       </c>
     </row>
     <row r="867">
@@ -10541,7 +10535,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.737114289450416</v>
+        <v>-0.181250966161148</v>
       </c>
     </row>
     <row r="868">
@@ -10552,7 +10546,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-3.42666968240589</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="869">
@@ -10563,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.666278887835449</v>
+        <v>-1.78127932155501</v>
       </c>
     </row>
     <row r="870">
@@ -10574,7 +10568,7 @@
         <v>16</v>
       </c>
       <c r="C870" t="n">
-        <v>0.137041583974819</v>
+        <v>0.491710474248266</v>
       </c>
     </row>
     <row r="871">
@@ -10585,7 +10579,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.162857832818618</v>
+        <v>-0.195848233059457</v>
       </c>
     </row>
     <row r="872">
@@ -10596,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.272243157903686</v>
+        <v>-0.110036884888975</v>
       </c>
     </row>
     <row r="873">
@@ -10629,7 +10623,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.264190898929398</v>
+        <v>-0.901555356957479</v>
       </c>
     </row>
     <row r="876">
@@ -10640,7 +10634,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.281793582647252</v>
+        <v>-0.193159125131425</v>
       </c>
     </row>
     <row r="877">
@@ -10651,7 +10645,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.21689058749149</v>
       </c>
     </row>
     <row r="878">
@@ -10684,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.257693664751559</v>
+        <v>-0.274749358931064</v>
       </c>
     </row>
     <row r="881">
@@ -10695,7 +10689,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>0.245222055049258</v>
+        <v>-1.39468573569362</v>
       </c>
     </row>
     <row r="882">
@@ -10706,7 +10700,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.49430864992307</v>
+        <v>-0.607509612564616</v>
       </c>
     </row>
     <row r="883">
@@ -10717,7 +10711,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>0.140166878473219</v>
+        <v>0.31751356693815</v>
       </c>
     </row>
     <row r="884">
@@ -10739,7 +10733,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.991371675953869</v>
+        <v>-0.663131968963395</v>
       </c>
     </row>
     <row r="886">
@@ -10750,7 +10744,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.36616063106307</v>
+        <v>-0.491437843003167</v>
       </c>
     </row>
     <row r="887">
@@ -10761,7 +10755,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.574463533009511</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="888">
@@ -10772,7 +10766,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.19488739643336</v>
+        <v>-0.278763486310304</v>
       </c>
     </row>
     <row r="889">
@@ -10783,7 +10777,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.406132837322182</v>
+        <v>-0.382413068086732</v>
       </c>
     </row>
     <row r="890">
@@ -10805,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.842210263059993</v>
+        <v>-0.368976159226191</v>
       </c>
     </row>
     <row r="892">
@@ -10816,7 +10810,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.879314091840344</v>
       </c>
     </row>
     <row r="893">
@@ -10827,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.4603241240156</v>
+        <v>-57.6858716972862</v>
       </c>
     </row>
     <row r="894">
@@ -10838,7 +10832,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-11.8124243039675</v>
+        <v>-1.99999606898668</v>
       </c>
     </row>
     <row r="895">
@@ -10849,7 +10843,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.346718544688239</v>
+        <v>-0.474483168067466</v>
       </c>
     </row>
     <row r="896">
@@ -10860,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.171599495901962</v>
+        <v>-0.275847716951247</v>
       </c>
     </row>
     <row r="897">
@@ -10871,7 +10865,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.420222995494726</v>
+        <v>-79.8920251514905</v>
       </c>
     </row>
     <row r="898">
@@ -10893,7 +10887,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.450123424790591</v>
+        <v>-0.224093127835643</v>
       </c>
     </row>
     <row r="900">
@@ -10904,7 +10898,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.254965764443487</v>
       </c>
     </row>
     <row r="901">
@@ -10915,7 +10909,7 @@
         <v>16</v>
       </c>
       <c r="C901" t="n">
-        <v>-1.07193709016615</v>
+        <v>-0.865806456557971</v>
       </c>
     </row>
     <row r="902">
@@ -10926,7 +10920,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-1.05241963761558</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="903">
@@ -10948,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.316890714174254</v>
+        <v>-0.249195185797336</v>
       </c>
     </row>
     <row r="905">
@@ -10959,7 +10953,7 @@
         <v>16</v>
       </c>
       <c r="C905" t="n">
-        <v>-0.222262715557652</v>
+        <v>-0.516553967134241</v>
       </c>
     </row>
     <row r="906">
@@ -10981,7 +10975,7 @@
         <v>16</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.156231488895971</v>
+        <v>-0.218583549135226</v>
       </c>
     </row>
     <row r="908">
@@ -10992,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-3.22262011523171</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="909">
@@ -11003,7 +10997,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.172623385358736</v>
+        <v>-0.510691573129594</v>
       </c>
     </row>
     <row r="910">
@@ -11014,7 +11008,7 @@
         <v>16</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.352496467707633</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="911">
@@ -11025,7 +11019,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.204271436844671</v>
+        <v>-0.210873865784128</v>
       </c>
     </row>
     <row r="912">
@@ -11080,7 +11074,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.198373473970042</v>
       </c>
     </row>
     <row r="917">
@@ -11091,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.28097476258206</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="918">
@@ -11102,7 +11096,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.485922839841599</v>
+        <v>-0.352970693744146</v>
       </c>
     </row>
     <row r="919">
@@ -11124,7 +11118,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.183065935413013</v>
+        <v>-0.191617027138951</v>
       </c>
     </row>
     <row r="921">
@@ -11146,7 +11140,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.20059312938292</v>
+        <v>-0.199126356694325</v>
       </c>
     </row>
     <row r="923">
@@ -11157,7 +11151,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.69082648621787</v>
+        <v>-0.341997751532642</v>
       </c>
     </row>
     <row r="924">
@@ -11168,7 +11162,7 @@
         <v>16</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.435107613583204</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="925">
@@ -11179,7 +11173,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-1.61608332859151</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="926">
@@ -11190,7 +11184,7 @@
         <v>16</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.629119082679821</v>
+        <v>-0.194339913683306</v>
       </c>
     </row>
     <row r="927">
@@ -11201,7 +11195,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.184616242601826</v>
+        <v>-0.241475103616348</v>
       </c>
     </row>
     <row r="928">
@@ -11223,7 +11217,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.141702529514736</v>
+        <v>-0.830572853538931</v>
       </c>
     </row>
     <row r="930">
@@ -11245,7 +11239,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.155362759834643</v>
+        <v>-0.170510426176107</v>
       </c>
     </row>
     <row r="932">
@@ -11267,7 +11261,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.800907012784608</v>
+        <v>-0.366982656525454</v>
       </c>
     </row>
     <row r="934">
@@ -11278,7 +11272,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.423849946102454</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="935">
@@ -11289,7 +11283,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>0.472606084114547</v>
+        <v>0.436706400053948</v>
       </c>
     </row>
     <row r="936">
@@ -11311,7 +11305,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.220026073511976</v>
+        <v>-0.165658930480608</v>
       </c>
     </row>
     <row r="938">
@@ -11322,7 +11316,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.305142085156322</v>
+        <v>-0.999421999799734</v>
       </c>
     </row>
     <row r="939">
@@ -11344,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>0.0365644048152745</v>
+        <v>-0.220257705215142</v>
       </c>
     </row>
     <row r="941">
@@ -11355,7 +11349,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.167858226832192</v>
+        <v>-0.68048560701601</v>
       </c>
     </row>
     <row r="942">
@@ -11366,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.853123712539393</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="943">
@@ -11377,7 +11371,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.790229264553293</v>
+        <v>-0.273268877304983</v>
       </c>
     </row>
     <row r="944">
@@ -11399,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.251108611566136</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="946">
@@ -11410,7 +11404,7 @@
         <v>16</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.275917798054753</v>
+        <v>-0.590151000937392</v>
       </c>
     </row>
     <row r="947">
@@ -11421,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.923699018136213</v>
+        <v>-0.285750245947759</v>
       </c>
     </row>
     <row r="948">
@@ -11432,7 +11426,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.792988781631483</v>
+        <v>-0.190373675706089</v>
       </c>
     </row>
     <row r="949">
@@ -11454,7 +11448,7 @@
         <v>16</v>
       </c>
       <c r="C950" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.34805792337627</v>
       </c>
     </row>
     <row r="951">
@@ -11487,7 +11481,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.340759111726415</v>
+        <v>-0.575436216674488</v>
       </c>
     </row>
     <row r="954">
@@ -11498,7 +11492,7 @@
         <v>16</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.84877558915078</v>
       </c>
     </row>
     <row r="955">
@@ -11509,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.19129939978131</v>
       </c>
     </row>
     <row r="956">
@@ -11520,7 +11514,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.327883052831478</v>
+        <v>-0.18237714031213</v>
       </c>
     </row>
     <row r="957">
@@ -11531,7 +11525,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-1.19932942389907</v>
+        <v>-0.197528478482533</v>
       </c>
     </row>
     <row r="958">
@@ -11553,7 +11547,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.845373374782626</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="960">
@@ -11586,7 +11580,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.44139349259361</v>
+        <v>-0.391053854858687</v>
       </c>
     </row>
     <row r="963">
@@ -11597,7 +11591,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.621874478361372</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="964">
@@ -11608,7 +11602,7 @@
         <v>16</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.101813247897062</v>
+        <v>-0.0664742867550769</v>
       </c>
     </row>
     <row r="965">
@@ -11619,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.227642664486457</v>
+        <v>-0.218113553253475</v>
       </c>
     </row>
     <row r="966">
@@ -11630,7 +11624,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.330276512850376</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="967">
@@ -11641,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.131465996245209</v>
+        <v>0.0998703576751486</v>
       </c>
     </row>
     <row r="968">
@@ -11663,7 +11657,7 @@
         <v>16</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.31603637210753</v>
       </c>
     </row>
     <row r="970">
@@ -11707,7 +11701,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-1.97332002476882</v>
+        <v>0.376695748385307</v>
       </c>
     </row>
     <row r="974">
@@ -11729,7 +11723,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.175307721465174</v>
+        <v>0.13967801057826</v>
       </c>
     </row>
     <row r="976">
@@ -11751,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.265036968607481</v>
+        <v>-0.185019363499862</v>
       </c>
     </row>
     <row r="978">
@@ -11762,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.269043081536857</v>
+        <v>-0.23548456585909</v>
       </c>
     </row>
     <row r="979">
@@ -11773,7 +11767,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-1.33180823754709</v>
+        <v>-8.9710997982275</v>
       </c>
     </row>
     <row r="980">
@@ -11806,7 +11800,7 @@
         <v>16</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.259071438162743</v>
+        <v>-0.252354348666594</v>
       </c>
     </row>
     <row r="983">
@@ -11817,7 +11811,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-1.38703767956538</v>
+        <v>-10.0698053446029</v>
       </c>
     </row>
     <row r="984">
@@ -11839,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>0.128594320711873</v>
+        <v>-0.30767774422343</v>
       </c>
     </row>
     <row r="986">
@@ -11861,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.244584959555516</v>
+        <v>-0.965073009549754</v>
       </c>
     </row>
     <row r="988">
@@ -11883,7 +11877,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.445254620637317</v>
+        <v>-0.229526672866736</v>
       </c>
     </row>
     <row r="990">
@@ -11916,7 +11910,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.343088701584349</v>
+        <v>-0.65534408177545</v>
       </c>
     </row>
     <row r="993">
@@ -11927,7 +11921,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.328514080501096</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="994">
@@ -11938,7 +11932,7 @@
         <v>16</v>
       </c>
       <c r="C994" t="n">
-        <v>-0.181953397898737</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="995">
@@ -11949,7 +11943,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.198098208271381</v>
       </c>
     </row>
     <row r="996">
@@ -11960,7 +11954,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-5.35408844298693</v>
+        <v>-0.898715852718657</v>
       </c>
     </row>
     <row r="997">
@@ -11982,7 +11976,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.0690503457376959</v>
+        <v>0.0313680245886563</v>
       </c>
     </row>
     <row r="999">
@@ -11993,7 +11987,7 @@
         <v>16</v>
       </c>
       <c r="C999" t="n">
-        <v>-0.175553284027327</v>
+        <v>-0.966757070352507</v>
       </c>
     </row>
     <row r="1000">
@@ -12004,7 +11998,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>0.536813486701221</v>
+        <v>0.076036130464552</v>
       </c>
     </row>
     <row r="1001">
@@ -12015,7 +12009,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.310950132062252</v>
+        <v>-1.6648119185346</v>
       </c>
     </row>
     <row r="1002">
@@ -12026,7 +12020,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.664980876830924</v>
+        <v>-37.3880677584926</v>
       </c>
     </row>
     <row r="1003">
@@ -12048,7 +12042,7 @@
         <v>16</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.39707025930241</v>
+        <v>-1.57735720754014</v>
       </c>
     </row>
     <row r="1005">
@@ -12059,7 +12053,7 @@
         <v>16</v>
       </c>
       <c r="C1005" t="n">
-        <v>0.0773173268890514</v>
+        <v>-0.532429218540329</v>
       </c>
     </row>
     <row r="1006">
@@ -12070,7 +12064,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>0.270683875353415</v>
+        <v>0.0995879286663471</v>
       </c>
     </row>
     <row r="1007">
@@ -12081,7 +12075,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.547309590325776</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1008">
@@ -12092,7 +12086,7 @@
         <v>16</v>
       </c>
       <c r="C1008" t="n">
-        <v>0.112731252328339</v>
+        <v>0.179458590836035</v>
       </c>
     </row>
     <row r="1009">
@@ -12103,7 +12097,7 @@
         <v>16</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.209464603465506</v>
       </c>
     </row>
     <row r="1010">
@@ -12114,7 +12108,7 @@
         <v>16</v>
       </c>
       <c r="C1010" t="n">
-        <v>0.230147070759509</v>
+        <v>-0.29271659031021</v>
       </c>
     </row>
     <row r="1011">
@@ -12136,7 +12130,7 @@
         <v>16</v>
       </c>
       <c r="C1012" t="n">
-        <v>-0.542106579632765</v>
+        <v>-0.348077035156958</v>
       </c>
     </row>
     <row r="1013">
@@ -12147,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.38786786152558</v>
+        <v>-0.176313979237087</v>
       </c>
     </row>
     <row r="1014">
@@ -12169,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.246215272071246</v>
+        <v>-0.164895346349726</v>
       </c>
     </row>
     <row r="1016">
@@ -12180,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.192319487845291</v>
+        <v>-0.213823726954732</v>
       </c>
     </row>
     <row r="1017">
@@ -12191,7 +12185,7 @@
         <v>16</v>
       </c>
       <c r="C1017" t="n">
-        <v>-1.07307808714685</v>
+        <v>-0.432521793952187</v>
       </c>
     </row>
     <row r="1018">
@@ -12213,7 +12207,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>-0.0481365046024222</v>
+        <v>-0.279797369996283</v>
       </c>
     </row>
     <row r="1020">
@@ -12224,7 +12218,7 @@
         <v>16</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.727142432459798</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1021">
@@ -12246,7 +12240,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.179772644810122</v>
+        <v>-11.0710289220185</v>
       </c>
     </row>
     <row r="1023">
@@ -12257,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.148786178286062</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1024">
@@ -12279,7 +12273,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.374372616259104</v>
+        <v>-0.624109452097162</v>
       </c>
     </row>
     <row r="1026">
@@ -12301,7 +12295,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-1.49733677035524</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1028">
@@ -12312,7 +12306,7 @@
         <v>16</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.256051413199923</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1029">
@@ -12323,7 +12317,7 @@
         <v>16</v>
       </c>
       <c r="C1029" t="n">
-        <v>-0.236794669200224</v>
+        <v>-0.171660607677573</v>
       </c>
     </row>
     <row r="1030">
@@ -12334,7 +12328,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.226089481914306</v>
+        <v>-0.240382054851057</v>
       </c>
     </row>
     <row r="1031">
@@ -12345,7 +12339,7 @@
         <v>16</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.299460820847799</v>
+        <v>-0.147002191242295</v>
       </c>
     </row>
     <row r="1032">
@@ -12367,7 +12361,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.187365842124086</v>
       </c>
     </row>
     <row r="1034">
@@ -12378,7 +12372,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.355315627525553</v>
+        <v>-0.541616761393343</v>
       </c>
     </row>
     <row r="1035">
@@ -12411,7 +12405,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>0.314839635974071</v>
+        <v>0.232769218475745</v>
       </c>
     </row>
     <row r="1038">
@@ -12422,7 +12416,7 @@
         <v>16</v>
       </c>
       <c r="C1038" t="n">
-        <v>-0.578603396731124</v>
+        <v>-0.863697270107777</v>
       </c>
     </row>
     <row r="1039">
@@ -12444,7 +12438,7 @@
         <v>16</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.973353736933995</v>
+        <v>-0.234842208715357</v>
       </c>
     </row>
     <row r="1041">
@@ -12455,7 +12449,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.146522061510979</v>
+        <v>-0.186359923265689</v>
       </c>
     </row>
     <row r="1042">
@@ -12477,7 +12471,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.491605019965529</v>
+        <v>-0.291680185921015</v>
       </c>
     </row>
     <row r="1044">
@@ -12488,7 +12482,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>0.193619996732009</v>
+        <v>-0.179928521729608</v>
       </c>
     </row>
     <row r="1045">
@@ -12499,7 +12493,7 @@
         <v>16</v>
       </c>
       <c r="C1045" t="n">
-        <v>-2.39054507761706</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1046">
@@ -12510,7 +12504,7 @@
         <v>16</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.33062575736652</v>
+        <v>-44.7954319262459</v>
       </c>
     </row>
     <row r="1047">
@@ -12532,7 +12526,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.0358878116015211</v>
+        <v>0.697765866571038</v>
       </c>
     </row>
     <row r="1049">
@@ -12543,7 +12537,7 @@
         <v>16</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.475598303602251</v>
       </c>
     </row>
     <row r="1050">
@@ -12554,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.40521527125708</v>
+        <v>-0.293239935984949</v>
       </c>
     </row>
     <row r="1051">
@@ -12565,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.179469022444056</v>
+        <v>-0.309525119482127</v>
       </c>
     </row>
     <row r="1052">
@@ -12576,7 +12570,7 @@
         <v>16</v>
       </c>
       <c r="C1052" t="n">
-        <v>-0.486869084736836</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1053">
@@ -12598,7 +12592,7 @@
         <v>16</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.107672474010742</v>
+        <v>-0.192442114921361</v>
       </c>
     </row>
     <row r="1055">
@@ -12609,7 +12603,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.445306055446992</v>
       </c>
     </row>
     <row r="1056">
@@ -12642,7 +12636,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.212157592472125</v>
       </c>
     </row>
     <row r="1059">
@@ -12653,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>-0.587072693793953</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1060">
@@ -12664,7 +12658,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>0.0465321557160767</v>
+        <v>-0.074847214960192</v>
       </c>
     </row>
     <row r="1061">
@@ -12686,7 +12680,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.635935225582712</v>
       </c>
     </row>
     <row r="1063">
@@ -12697,7 +12691,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.517742805509781</v>
+        <v>-1.24872802894643</v>
       </c>
     </row>
     <row r="1064">
@@ -12708,7 +12702,7 @@
         <v>16</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.378257033178839</v>
+        <v>-0.177928461381511</v>
       </c>
     </row>
     <row r="1065">
@@ -12730,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.253517930028499</v>
+        <v>-2.79598526533109</v>
       </c>
     </row>
     <row r="1067">
@@ -12752,7 +12746,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.256173028063366</v>
+        <v>-1.90419086019891</v>
       </c>
     </row>
     <row r="1069">
@@ -12763,7 +12757,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.369799117463653</v>
+        <v>-0.179025145707126</v>
       </c>
     </row>
     <row r="1070">
@@ -12774,7 +12768,7 @@
         <v>16</v>
       </c>
       <c r="C1070" t="n">
-        <v>0.21211814744461</v>
+        <v>0.140442406818249</v>
       </c>
     </row>
     <row r="1071">
@@ -12785,7 +12779,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.263664680947343</v>
+        <v>-0.189213249194376</v>
       </c>
     </row>
     <row r="1072">
@@ -12796,7 +12790,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.193942192991873</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1073">
@@ -12807,7 +12801,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.159763313609467</v>
+        <v>-37.7778204678089</v>
       </c>
     </row>
     <row r="1074">
@@ -12818,7 +12812,7 @@
         <v>16</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.11278424252365</v>
       </c>
     </row>
     <row r="1075">
@@ -12829,7 +12823,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.226811968372885</v>
+        <v>-0.257074347093322</v>
       </c>
     </row>
     <row r="1076">
@@ -12840,7 +12834,7 @@
         <v>16</v>
       </c>
       <c r="C1076" t="n">
-        <v>-0.16657427589669</v>
+        <v>-0.173016916449981</v>
       </c>
     </row>
     <row r="1077">
@@ -12862,7 +12856,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.204743657388421</v>
+        <v>-0.987021966164395</v>
       </c>
     </row>
     <row r="1079">
@@ -12873,7 +12867,7 @@
         <v>16</v>
       </c>
       <c r="C1079" t="n">
-        <v>-1.03601741905017</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1080">
@@ -12884,7 +12878,7 @@
         <v>16</v>
       </c>
       <c r="C1080" t="n">
-        <v>-0.428592000742052</v>
+        <v>-0.261506214156193</v>
       </c>
     </row>
     <row r="1081">
@@ -12895,7 +12889,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>0.0656927201739966</v>
+        <v>0.089660820476691</v>
       </c>
     </row>
     <row r="1082">
@@ -12928,7 +12922,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.216125046110454</v>
+        <v>-0.191949818026034</v>
       </c>
     </row>
     <row r="1085">
@@ -12939,7 +12933,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.2483264026449</v>
       </c>
     </row>
     <row r="1086">
@@ -12972,7 +12966,7 @@
         <v>16</v>
       </c>
       <c r="C1088" t="n">
-        <v>-0.398409888619365</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1089">
@@ -12983,7 +12977,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.389684607812835</v>
+        <v>0.208020134426038</v>
       </c>
     </row>
     <row r="1090">
@@ -13005,7 +12999,7 @@
         <v>16</v>
       </c>
       <c r="C1091" t="n">
-        <v>-0.0143680535729831</v>
+        <v>0.225867613592857</v>
       </c>
     </row>
     <row r="1092">
@@ -13016,7 +13010,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.251299167667788</v>
+        <v>-0.415303668352298</v>
       </c>
     </row>
     <row r="1093">
@@ -13027,7 +13021,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.195173488396179</v>
+        <v>-0.204720882116743</v>
       </c>
     </row>
     <row r="1094">
@@ -13038,7 +13032,7 @@
         <v>16</v>
       </c>
       <c r="C1094" t="n">
-        <v>-0.0971141279300858</v>
+        <v>-1.57182653939346</v>
       </c>
     </row>
     <row r="1095">
@@ -13049,7 +13043,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.107249302492967</v>
+        <v>-53.7859062254004</v>
       </c>
     </row>
     <row r="1096">
@@ -13060,7 +13054,7 @@
         <v>16</v>
       </c>
       <c r="C1096" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.29461005976167</v>
       </c>
     </row>
     <row r="1097">
@@ -13071,7 +13065,7 @@
         <v>16</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.159763313609468</v>
+        <v>-3.63988935608586</v>
       </c>
     </row>
     <row r="1098">
@@ -13082,7 +13076,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.159763313609468</v>
+        <v>-23.382027628464</v>
       </c>
     </row>
     <row r="1099">
@@ -13093,7 +13087,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.11350562372595</v>
+        <v>-0.43499945893293</v>
       </c>
     </row>
     <row r="1100">
@@ -13104,7 +13098,7 @@
         <v>16</v>
       </c>
       <c r="C1100" t="n">
-        <v>0.135712862386576</v>
+        <v>-0.909546707385009</v>
       </c>
     </row>
     <row r="1101">
@@ -13115,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.83550389983027</v>
+        <v>-3.5616692448779</v>
       </c>
     </row>
     <row r="1102">
@@ -13137,7 +13131,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.792530180868212</v>
       </c>
     </row>
     <row r="1104">
@@ -13148,7 +13142,7 @@
         <v>16</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.0506324253923154</v>
+        <v>-0.225384678347476</v>
       </c>
     </row>
     <row r="1105">
@@ -13159,7 +13153,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.387348164172987</v>
       </c>
     </row>
     <row r="1106">
@@ -13170,7 +13164,7 @@
         <v>16</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.209470548750364</v>
+        <v>-0.0888129258971522</v>
       </c>
     </row>
     <row r="1107">
@@ -13181,7 +13175,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-1.15084705007899</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1108">
@@ -13203,7 +13197,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-0.159763313609467</v>
+        <v>-38.3870354369099</v>
       </c>
     </row>
     <row r="1110">
@@ -13214,7 +13208,7 @@
         <v>16</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.44183022759995</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1111">
@@ -13225,7 +13219,7 @@
         <v>16</v>
       </c>
       <c r="C1111" t="n">
-        <v>-2.63341002658972</v>
+        <v>-0.431136229459479</v>
       </c>
     </row>
     <row r="1112">
@@ -13269,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.432055815192521</v>
+        <v>-0.387539473517986</v>
       </c>
     </row>
     <row r="1116">
@@ -13280,7 +13274,7 @@
         <v>16</v>
       </c>
       <c r="C1116" t="n">
-        <v>-0.273746151916885</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1117">
@@ -13291,7 +13285,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.32168325026399</v>
       </c>
     </row>
     <row r="1118">
@@ -13313,7 +13307,7 @@
         <v>16</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.196653245599715</v>
+        <v>0.0511128418671307</v>
       </c>
     </row>
     <row r="1120">
@@ -13324,7 +13318,7 @@
         <v>16</v>
       </c>
       <c r="C1120" t="n">
-        <v>-0.169006533779391</v>
+        <v>0.109435301696712</v>
       </c>
     </row>
     <row r="1121">
@@ -13335,7 +13329,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.330960713353699</v>
+        <v>-0.148145067988565</v>
       </c>
     </row>
     <row r="1122">
@@ -13379,7 +13373,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>-0.549997263697253</v>
+        <v>-0.313947744799062</v>
       </c>
     </row>
     <row r="1126">
@@ -13412,7 +13406,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.813198485693983</v>
+        <v>-0.148912073604839</v>
       </c>
     </row>
     <row r="1129">
@@ -13423,7 +13417,7 @@
         <v>16</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.164245520460988</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1130">
@@ -13434,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.0248707544468509</v>
+        <v>-110.793842871701</v>
       </c>
     </row>
     <row r="1131">
@@ -13445,7 +13439,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.696097992746903</v>
+        <v>-0.730430109387419</v>
       </c>
     </row>
     <row r="1132">
@@ -13456,7 +13450,7 @@
         <v>16</v>
       </c>
       <c r="C1132" t="n">
-        <v>-0.159763313609467</v>
+        <v>-2.48508561881767</v>
       </c>
     </row>
     <row r="1133">
@@ -13467,7 +13461,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.673131630047335</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1134">
@@ -13500,7 +13494,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.266788318830859</v>
+        <v>-0.229164889863612</v>
       </c>
     </row>
     <row r="1137">
@@ -13533,7 +13527,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.194276663835785</v>
+        <v>-1.13927893481461</v>
       </c>
     </row>
     <row r="1140">
@@ -13555,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.256017670899025</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1142">
@@ -13566,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.206987377124039</v>
+        <v>-0.470691124936782</v>
       </c>
     </row>
     <row r="1143">
@@ -13588,7 +13582,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.246441742039871</v>
       </c>
     </row>
     <row r="1145">
@@ -13599,7 +13593,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.32157853078179</v>
       </c>
     </row>
     <row r="1146">
@@ -13621,7 +13615,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.190856734465458</v>
+        <v>-0.229918810361208</v>
       </c>
     </row>
     <row r="1148">
@@ -13643,7 +13637,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.113364079125225</v>
       </c>
     </row>
     <row r="1150">
@@ -13687,7 +13681,7 @@
         <v>16</v>
       </c>
       <c r="C1153" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.861703903134239</v>
       </c>
     </row>
     <row r="1154">
@@ -13698,7 +13692,7 @@
         <v>16</v>
       </c>
       <c r="C1154" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.436228095334654</v>
       </c>
     </row>
     <row r="1155">
@@ -13720,7 +13714,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.731075207043215</v>
+        <v>-0.268555132148679</v>
       </c>
     </row>
     <row r="1157">
@@ -13742,7 +13736,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.599197155511012</v>
+        <v>-0.602263545354753</v>
       </c>
     </row>
     <row r="1159">
@@ -13764,7 +13758,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.0441260062787741</v>
+        <v>-0.221989866227195</v>
       </c>
     </row>
     <row r="1161">
@@ -13797,7 +13791,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.52424958060565</v>
+        <v>-0.196177668055098</v>
       </c>
     </row>
     <row r="1164">
@@ -13808,7 +13802,7 @@
         <v>16</v>
       </c>
       <c r="C1164" t="n">
-        <v>-0.615016216384737</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1165">
@@ -13819,7 +13813,7 @@
         <v>16</v>
       </c>
       <c r="C1165" t="n">
-        <v>-1.07700675952002</v>
+        <v>-5.73578667394584</v>
       </c>
     </row>
     <row r="1166">
@@ -13830,7 +13824,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.381632396079784</v>
       </c>
     </row>
     <row r="1167">
@@ -13841,7 +13835,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>0.0141531799053127</v>
+        <v>-0.145405879122046</v>
       </c>
     </row>
     <row r="1168">
@@ -13863,7 +13857,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.419675036484431</v>
       </c>
     </row>
     <row r="1170">
@@ -13874,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-1.72790517431857</v>
+        <v>-6.14216906293441</v>
       </c>
     </row>
     <row r="1171">
@@ -13885,7 +13879,7 @@
         <v>16</v>
       </c>
       <c r="C1171" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.307497839627048</v>
       </c>
     </row>
     <row r="1172">
@@ -13896,7 +13890,7 @@
         <v>16</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.08314526820695</v>
       </c>
     </row>
     <row r="1173">
@@ -13907,7 +13901,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.320255562353994</v>
+        <v>-0.244131706563565</v>
       </c>
     </row>
     <row r="1174">
@@ -13918,7 +13912,7 @@
         <v>16</v>
       </c>
       <c r="C1174" t="n">
-        <v>-0.760628666136918</v>
+        <v>-0.243303019923076</v>
       </c>
     </row>
     <row r="1175">
@@ -13929,7 +13923,7 @@
         <v>16</v>
       </c>
       <c r="C1175" t="n">
-        <v>-0.0103117473590637</v>
+        <v>-0.0958410433771324</v>
       </c>
     </row>
     <row r="1176">
@@ -13940,7 +13934,7 @@
         <v>16</v>
       </c>
       <c r="C1176" t="n">
-        <v>-1.35389801399648</v>
+        <v>-4.29155116452556</v>
       </c>
     </row>
     <row r="1177">
@@ -13984,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.794100163023311</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1181">
@@ -13995,7 +13989,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.178031409120469</v>
+        <v>-0.302972369245311</v>
       </c>
     </row>
     <row r="1182">
@@ -14006,7 +14000,7 @@
         <v>16</v>
       </c>
       <c r="C1182" t="n">
-        <v>-0.220698198012012</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1183">
@@ -14028,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-2.04042194495146</v>
+        <v>-0.353517157123211</v>
       </c>
     </row>
     <row r="1185">
@@ -14050,7 +14044,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.154344008042132</v>
+        <v>-0.168038156713445</v>
       </c>
     </row>
     <row r="1187">
@@ -14061,7 +14055,7 @@
         <v>16</v>
       </c>
       <c r="C1187" t="n">
-        <v>-0.23552845177755</v>
+        <v>-16.5764878308357</v>
       </c>
     </row>
     <row r="1188">
@@ -14072,7 +14066,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.159763313609467</v>
+        <v>-13.0355703709845</v>
       </c>
     </row>
     <row r="1189">
@@ -14083,7 +14077,7 @@
         <v>16</v>
       </c>
       <c r="C1189" t="n">
-        <v>-0.32686377404446</v>
+        <v>-0.448996073778816</v>
       </c>
     </row>
     <row r="1190">
@@ -14094,7 +14088,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-1.68667187309824</v>
+        <v>-1.73875562915709</v>
       </c>
     </row>
     <row r="1191">
@@ -14105,7 +14099,7 @@
         <v>16</v>
       </c>
       <c r="C1191" t="n">
-        <v>-4.80881877787135</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1192">
@@ -14127,7 +14121,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.987205405269165</v>
+        <v>-0.0339450542034123</v>
       </c>
     </row>
     <row r="1194">
@@ -14149,7 +14143,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>-0.27150962298465</v>
+        <v>-0.466943385705573</v>
       </c>
     </row>
     <row r="1196">
@@ -14160,7 +14154,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.328744098604214</v>
+        <v>-0.695930826120261</v>
       </c>
     </row>
     <row r="1197">
@@ -14171,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.725873302411151</v>
+        <v>-0.47995367383313</v>
       </c>
     </row>
     <row r="1198">
@@ -14182,7 +14176,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.118398454581975</v>
+        <v>-0.211564075656504</v>
       </c>
     </row>
     <row r="1199">
@@ -14193,7 +14187,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.178535102326108</v>
+        <v>-0.212401082060519</v>
       </c>
     </row>
     <row r="1200">
@@ -14204,7 +14198,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.26548685632717</v>
+        <v>-0.356405498009666</v>
       </c>
     </row>
     <row r="1201">
@@ -14215,7 +14209,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-0.181510439070316</v>
+        <v>-0.169243349920235</v>
       </c>
     </row>
   </sheetData>
@@ -14328,7 +14322,7 @@
         <v>14.93</v>
       </c>
       <c r="E6" t="n">
-        <v>25.9530849683287</v>
+        <v>33.6826993325124</v>
       </c>
     </row>
     <row r="7">
@@ -14362,7 +14356,7 @@
         <v>8.06</v>
       </c>
       <c r="E8" t="n">
-        <v>0.922968857100184</v>
+        <v>1.24606292358093</v>
       </c>
     </row>
     <row r="9">
@@ -14447,7 +14441,7 @@
         <v>-1.86</v>
       </c>
       <c r="E13" t="n">
-        <v>8.77807979360832</v>
+        <v>8.48215984847747</v>
       </c>
     </row>
     <row r="14">
@@ -14464,7 +14458,7 @@
         <v>-6.6</v>
       </c>
       <c r="E14" t="n">
-        <v>5.44434946586647</v>
+        <v>5.34738880012885</v>
       </c>
     </row>
     <row r="15">
@@ -14566,7 +14560,7 @@
         <v>274.62</v>
       </c>
       <c r="E20" t="n">
-        <v>-2777.48330024814</v>
+        <v>-3246.25523392378</v>
       </c>
     </row>
     <row r="21">
@@ -14702,7 +14696,7 @@
         <v>-2646.36</v>
       </c>
       <c r="E28" t="n">
-        <v>262.450609612814</v>
+        <v>216.467911328422</v>
       </c>
     </row>
     <row r="29">
@@ -14736,7 +14730,7 @@
         <v>-2594.04</v>
       </c>
       <c r="E30" t="n">
-        <v>-25.7157142857143</v>
+        <v>108.635158497596</v>
       </c>
     </row>
     <row r="31">
@@ -14821,7 +14815,7 @@
         <v>739.459999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-17.435</v>
+        <v>-4195.91701693116</v>
       </c>
     </row>
     <row r="36">
@@ -14957,7 +14951,7 @@
         <v>-2305.05</v>
       </c>
       <c r="E43" t="n">
-        <v>314.860009553101</v>
+        <v>317.697737334063</v>
       </c>
     </row>
     <row r="44">
@@ -15093,7 +15087,7 @@
         <v>2.983</v>
       </c>
       <c r="E51" t="n">
-        <v>4.3704947493933</v>
+        <v>4.06067975046976</v>
       </c>
     </row>
     <row r="52">
@@ -15127,7 +15121,7 @@
         <v>3.879</v>
       </c>
       <c r="E53" t="n">
-        <v>1.3193077765507</v>
+        <v>1.17388062168173</v>
       </c>
     </row>
     <row r="54">
@@ -15722,7 +15716,7 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>10.6153846153846</v>
+        <v>15.4359247187313</v>
       </c>
     </row>
     <row r="89">
@@ -15832,10 +15826,10 @@
         <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -15857,19 +15851,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -15880,13 +15874,13 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -15897,13 +15891,13 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -15914,13 +15908,13 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -15931,13 +15925,13 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -15948,13 +15942,13 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -15965,7 +15959,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -15982,7 +15976,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -15999,7 +15993,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -16027,30 +16021,30 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -16061,13 +16055,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -16095,30 +16089,30 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -16129,19 +16123,257 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.0714285714285714</v>
       </c>
     </row>
   </sheetData>
